--- a/Paper Collections.xlsx
+++ b/Paper Collections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\Awesome-Interpretable-Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25D1A2B-B372-4C4B-87F1-13E17A74A85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B55627-3E51-4D89-9482-CA6EBB03A244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4752" yWindow="120" windowWidth="24564" windowHeight="16152" activeTab="5" xr2:uid="{DC4A0462-C16D-4CCA-9144-463242733AF6}"/>
+    <workbookView xWindow="4752" yWindow="120" windowWidth="24564" windowHeight="16152" firstSheet="1" activeTab="9" xr2:uid="{DC4A0462-C16D-4CCA-9144-463242733AF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Attribution-based" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Text" sheetId="7" r:id="rId7"/>
     <sheet name="Graph" sheetId="8" r:id="rId8"/>
     <sheet name="DRL" sheetId="9" r:id="rId9"/>
+    <sheet name="Evaluation" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,305 +43,41 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="189">
-  <si>
-    <t>Rationalizing Neural Predictions</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="262">
   <si>
     <t>EMNLP</t>
   </si>
   <si>
-    <t>From softmax to sparsemax: A sparse model of attention and multi-label classification</t>
-  </si>
-  <si>
     <t>ICML</t>
   </si>
   <si>
-    <t>Neural interaction transparency (nit): Disentangling learned interactions for improved interpretability</t>
-  </si>
-  <si>
     <t>NeurIPS</t>
   </si>
   <si>
-    <t>INVASE: Instance-wise variable selection using neural networks</t>
-  </si>
-  <si>
     <t>ICLR</t>
   </si>
   <si>
-    <t>Learning to explain: An information-theoretic perspective on model interpretation</t>
-  </si>
-  <si>
-    <t>Approximating CNNs with Bag-of-local-Features models works surprisingly well on ImageNet</t>
-  </si>
-  <si>
-    <t>Towards robust interpretability with self-explaining neural networks</t>
-  </si>
-  <si>
-    <t>Beyond Polarity: Interpretable Financial Sentiment Analysis with Hierarchical Query-driven Attention</t>
-  </si>
-  <si>
     <t>IJCAI</t>
   </si>
   <si>
-    <t>Interpretable multi-task learning for product quality prediction with attention mechanism</t>
-  </si>
-  <si>
-    <t>Adaptively Sparse Transformers</t>
-  </si>
-  <si>
-    <t>Exploiting kernel sparsity and entropy for interpretable CNN compression</t>
-  </si>
-  <si>
     <t>CVPR</t>
   </si>
   <si>
-    <t>Learning representations for neural network-based classification using the information bottleneck principle</t>
-  </si>
-  <si>
-    <t>Interpretable predictive modeling for climate variables with weighted lasso</t>
-  </si>
-  <si>
     <t>AAAI</t>
   </si>
   <si>
-    <t>Attention is not not Explanation</t>
-  </si>
-  <si>
-    <t>Is Attention Interpretable?</t>
-  </si>
-  <si>
     <t>ACL</t>
   </si>
   <si>
-    <t>Concrete autoencoders: Differentiable feature selection and reconstruction</t>
-  </si>
-  <si>
-    <t>Deepcoda: personalized interpretability for compositional health data</t>
-  </si>
-  <si>
-    <t>Graph Information Bottleneck for Subgraph Recognition</t>
-  </si>
-  <si>
-    <t>Sparse shrunk additive models</t>
-  </si>
-  <si>
-    <t>MRI reconstruction with interpretable pixel-wise operations using reinforcement learning</t>
-  </si>
-  <si>
-    <t>Attention is Not Only a Weight: Analyzing Transformers with Vector Norms</t>
-  </si>
-  <si>
-    <t>Modeling users' behavior sequences with hierarchical explainable network for cross-domain fraud detection</t>
-  </si>
-  <si>
-    <t>Feature selection using stochastic gates</t>
-  </si>
-  <si>
-    <t>On Identifiability in Transformers</t>
-  </si>
-  <si>
-    <t>Consistent feature selection for analytic deep neural networks</t>
-  </si>
-  <si>
-    <t>Towards Transparent and Explainable Attention Models</t>
-  </si>
-  <si>
-    <t>Learning to Deceive with Attention-Based Explanations</t>
-  </si>
-  <si>
-    <t>Timeshap: Explaining recurrent models through sequence perturbations</t>
-  </si>
-  <si>
-    <t>GAMI-Net: An explainable neural network based on generalized additive models with structured interactions</t>
-  </si>
-  <si>
-    <t>Pattern Recognit.</t>
-  </si>
-  <si>
-    <t>Shapley Explanation Networks</t>
-  </si>
-  <si>
-    <t>Market-oriented job skill valuation with cooperative composition neural network</t>
-  </si>
-  <si>
-    <t>Nat. Commun.</t>
-  </si>
-  <si>
-    <t>Neural additive models: Interpretable machine learning with neural nets</t>
-  </si>
-  <si>
-    <t>Is Sparse Attention more Interpretable?</t>
-  </si>
-  <si>
-    <t>Edge: Explaining deep reinforcement learning policies</t>
-  </si>
-  <si>
-    <t>Why attentions may not be interpretable?</t>
-  </si>
-  <si>
-    <t>Attention-based interpretability with concept transformers</t>
-  </si>
-  <si>
-    <t>Effective Attention Sheds Light On Interpretability</t>
-  </si>
-  <si>
-    <t>Self-Interpretable Model with Transformation Equivariant Interpretation</t>
-  </si>
-  <si>
-    <t>Towards rigorous interpretations: a formalisation of feature attribution</t>
-  </si>
-  <si>
-    <t>Discerning decision-making process of deep neural networks with hierarchical voting transformation</t>
-  </si>
-  <si>
-    <t>Recognizing predictive substructures with subgraph information bottleneck</t>
-  </si>
-  <si>
-    <t>Tabnet: Attentive interpretable tabular learning</t>
-  </si>
-  <si>
-    <t>Lassonet: A neural network with feature sparsity</t>
-  </si>
-  <si>
-    <t>Convolutional dynamic alignment networks for interpretable classifications</t>
-  </si>
-  <si>
-    <t>Have We Learned to Explain?: How Interpretability Methods Can Learn to Encode Predictions in their Interpretations</t>
-  </si>
-  <si>
     <t>AISTATS</t>
   </si>
   <si>
-    <t>Evidence-aware hierarchical interactive attention networks for explainable claim verification</t>
-  </si>
-  <si>
-    <t>Towards improved and interpretable deep metric learning via attentive grouping</t>
-  </si>
-  <si>
-    <t>Supervising model attention with human explanations for robust natural language inference</t>
-  </si>
-  <si>
-    <t>Deep Variational Information Bottleneck</t>
-  </si>
-  <si>
-    <t>Locally sparse neural networks for tabular biomedical data</t>
-  </si>
-  <si>
-    <t>Self-explaining deep models with logic rule reasoning</t>
-  </si>
-  <si>
-    <t>Is attention explanation? an introduction to the debate</t>
-  </si>
-  <si>
-    <t>Puregam: Learning an inherently pure additive model</t>
-  </si>
-  <si>
     <t>KDD</t>
   </si>
   <si>
-    <t>Query and attention augmentation for knowledge-based explainable reasoning</t>
-  </si>
-  <si>
-    <t>A diversified attention model for interpretable multiple clusterings</t>
-  </si>
-  <si>
-    <t>Interpretable and generalizable graph learning via stochastic attention mechanism</t>
-  </si>
-  <si>
-    <t>Neural basis models for interpretability</t>
-  </si>
-  <si>
-    <t>B-cos networks: Alignment is all we need for interpretability</t>
-  </si>
-  <si>
-    <t>Sparse interaction additive networks via feature interaction detection and sparse selection</t>
-  </si>
-  <si>
-    <t>Scalable interpretability via polynomials</t>
-  </si>
-  <si>
-    <t>Seat: stable and explainable attention</t>
-  </si>
-  <si>
-    <t>Interpretable bilinear attention network with domain adaptation improves drug--target prediction</t>
-  </si>
-  <si>
-    <t>Nat. Mach. Intell.</t>
-  </si>
-  <si>
-    <t>Extractive explanations for interpretable text ranking</t>
-  </si>
-  <si>
-    <t>Improving interpretability via explicit word interaction graph layer</t>
-  </si>
-  <si>
-    <t>Interpretable Geometric Deep Learning via Learnable Randomness Injection</t>
-  </si>
-  <si>
-    <t>Towards Faithful Neural Network Intrinsic Interpretation with Shapley Additive Self-Attribution</t>
-  </si>
-  <si>
-    <t>The contextual lasso: Sparse linear models via deep neural networks</t>
-  </si>
-  <si>
-    <t>Learning Faithful Attention for Interpretable Classification of Crisis-Related Microblogs under Constrained Human Budget</t>
-  </si>
-  <si>
-    <t>Improving Neural Additive Models with Bayesian Principles</t>
-  </si>
-  <si>
-    <t>Sparse Neural Additive Model: Interpretable Deep Learning with Feature Selection via Group Sparsity</t>
-  </si>
-  <si>
-    <t>CAT: Interpretable Concept-based Taylor Additive Models</t>
-  </si>
-  <si>
-    <t>B-cos Alignment for Inherently Interpretable CNNs and Vision Transformers</t>
-  </si>
-  <si>
-    <t>Kan: Kolmogorov-arnold networks</t>
-  </si>
-  <si>
-    <t>ProtoGate: Prototype-based Neural Networks with Global-to-local Feature Selection for Tabular Biomedical Data</t>
-  </si>
-  <si>
-    <t>InterpreTabNet: Distilling Predictive Signals from Tabular Data by Salient Feature Interpretation</t>
-  </si>
-  <si>
-    <t>Interpretable prototype-based graph information bottleneck</t>
-  </si>
-  <si>
-    <t>Exgc: Bridging efficiency and explainability in graph condensation</t>
-  </si>
-  <si>
-    <t>Towards self-interpretable graph-level anomaly detection</t>
-  </si>
-  <si>
-    <t>Tempme: Towards the explainability of temporal graph neural networks via motif discovery</t>
-  </si>
-  <si>
-    <t>NODE-GAM: Neural Generalized Additive Model for Interpretable Deep Learning</t>
-  </si>
-  <si>
-    <t>GRAND-SLAMIN'Interpretable Additive Modeling with Structural Constraints</t>
-  </si>
-  <si>
-    <t>Propagation Structure-Aware Graph Transformer for Robust and Interpretable Fake News Detection</t>
-  </si>
-  <si>
-    <t>NAISR: A 3D Neural Additive Model for Interpretable Shape Representation</t>
-  </si>
-  <si>
-    <t>Comprehensive Attribution: Inherently Explainable Vision Model with Feature Detector</t>
-  </si>
-  <si>
     <t>ECCV</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>Year</t>
   </si>
   <si>
@@ -365,250 +102,733 @@
     <t>ArXiv</t>
   </si>
   <si>
-    <t>NA2Q: Neural Attention Additive Model for Interpretable Multi-Agent Q-Learning</t>
-  </si>
-  <si>
     <t>TOIS</t>
   </si>
   <si>
     <t>TKDE</t>
   </si>
   <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Learning equations for extrapolation and control</t>
-  </si>
-  <si>
-    <t>Integration of neural network-based symbolic regression in deep learning for scientific discovery</t>
-  </si>
-  <si>
-    <t>Neural symbolic regression that scales</t>
-  </si>
-  <si>
-    <t>Symbolicgpt: A generative transformer model for symbolic regression</t>
-  </si>
-  <si>
-    <t>End-to-end symbolic regression with transformers</t>
-  </si>
-  <si>
-    <t>A unified framework for deep symbolic regression</t>
-  </si>
-  <si>
-    <t>Controllable neural symbolic regression</t>
-  </si>
-  <si>
-    <t>Deep Generative Symbolic Regression</t>
-  </si>
-  <si>
-    <t>GINN-LP: A Growing Interpretable Neural Network for Discovering Multivariate Laurent Polynomial Equations</t>
-  </si>
-  <si>
     <t>TNNLS</t>
   </si>
   <si>
-    <t>Concept bottleneck models</t>
-  </si>
-  <si>
-    <t>Concept whitening for interpretable image recognition</t>
-  </si>
-  <si>
-    <t>Explainable neural networks that simulate reasoning</t>
-  </si>
-  <si>
-    <t>Nat. Comput. Sci.</t>
-  </si>
-  <si>
-    <t>Post-hoc Concept Bottleneck Models</t>
-  </si>
-  <si>
-    <t>Concept embedding models: Beyond the accuracy-explainability trade-off</t>
-  </si>
-  <si>
-    <t>Addressing leakage in concept bottleneck models</t>
-  </si>
-  <si>
-    <t>Probabilistic Concept Bottleneck Models</t>
-  </si>
-  <si>
-    <t>Learning to Intervene on Concept Bottlenecks</t>
-  </si>
-  <si>
-    <t>Interactive concept bottleneck models</t>
-  </si>
-  <si>
-    <t>Label-free Concept Bottleneck Models</t>
-  </si>
-  <si>
-    <t>Language in a bottle: Language model guided concept bottlenecks for interpretable image classification</t>
-  </si>
-  <si>
-    <t>Towards Trustable Skin Cancer Diagnosis via Rewriting Model's Decision</t>
-  </si>
-  <si>
-    <t>Pantypes: Diverse Representatives for Self-Explainable Models</t>
-  </si>
-  <si>
-    <t>VLG-CBM: Training Concept Bottleneck Models with Vision-Language Guidance</t>
-  </si>
-  <si>
-    <t>Energy-based concept bottleneck models: unifying prediction, concept intervention, and conditional interpretations</t>
-  </si>
-  <si>
-    <t>Mica: Towards explainable skin lesion diagnosis via multi-level image-concept alignment</t>
-  </si>
-  <si>
-    <t>Relational Concept Bottleneck Models</t>
-  </si>
-  <si>
-    <t>Stochastic Concept Bottleneck Models</t>
-  </si>
-  <si>
-    <t>Learning to receive help: Intervention-aware concept embedding models</t>
-  </si>
-  <si>
-    <t>Incremental residual concept bottleneck models</t>
-  </si>
-  <si>
-    <t>Understanding Inter-Concept Relationships in Concept-Based Models</t>
-  </si>
-  <si>
-    <t>Coarse-to-fine concept bottleneck models</t>
-  </si>
-  <si>
-    <t>This looks like that: deep learning for interpretable image recognition</t>
-  </si>
-  <si>
-    <t>Interpretable and steerable sequence learning via prototypes</t>
-  </si>
-  <si>
-    <t>Neural prototype trees for interpretable fine-grained image recognition</t>
-  </si>
-  <si>
-    <t>Interpretable image recognition by constructing transparent embedding space</t>
-  </si>
-  <si>
-    <t>Protopshare: Prototypical parts sharing for similarity discovery in interpretable image classification</t>
-  </si>
-  <si>
-    <t>XProtoNet: diagnosis in chest radiography with global and local explanations</t>
-  </si>
-  <si>
-    <t>Proto2Proto: Can you recognize the car, the way I do?</t>
-  </si>
-  <si>
-    <t>Interpretable image classification with differentiable prototypes assignment</t>
-  </si>
-  <si>
-    <t>Protgnn: Towards self-explaining graph neural networks</t>
-  </si>
-  <si>
-    <t>Protovae: A trustworthy self-explainable prototypical variational model</t>
-  </si>
-  <si>
-    <t>ProtoryNet-Interpretable Text Classification Via Prototype Trajectories</t>
-  </si>
-  <si>
-    <t>PIP-Net: Patch-Based Intuitive Prototypes for Interpretable Image Classification</t>
-  </si>
-  <si>
-    <t>Towards interpretable deep reinforcement learning with human-friendly prototypes</t>
-  </si>
-  <si>
-    <t>Learning Support and Trivial Prototypes for Interpretable Image Classification</t>
-  </si>
-  <si>
-    <t>Concept-level debugging of part-prototype networks</t>
-  </si>
-  <si>
-    <t>Protoseg: Interpretable semantic segmentation with prototypical parts</t>
-  </si>
-  <si>
-    <t>This looks like those: Illuminating prototypical concepts using multiple visualizations</t>
-  </si>
-  <si>
-    <t>Market-aware Long-term Job Skill Recommendation with Explainable Deep Reinforcement Learning</t>
-  </si>
-  <si>
     <t>ICCV</t>
   </si>
   <si>
     <t>WACV</t>
   </si>
   <si>
-    <t>Logic Tensor Networks for Semantic Image Interpretation</t>
-  </si>
-  <si>
-    <t>Deep neural decision trees</t>
-  </si>
-  <si>
-    <t>Deep neural networks constrained by decision rules</t>
-  </si>
-  <si>
-    <t>NBDT: Neural-Backed Decision Tree</t>
-  </si>
-  <si>
-    <t>Transparent classification with multilayer logical perceptrons and random binarization</t>
-  </si>
-  <si>
-    <t>Human-driven FOL explanations of deep learning</t>
-  </si>
-  <si>
-    <t>A constraint-based approach to learning and explanation</t>
-  </si>
-  <si>
-    <t>Learning accurate and interpretable decision rule sets from neural networks</t>
-  </si>
-  <si>
-    <t>Scalable rule-based representation learning for interpretable classification</t>
-  </si>
-  <si>
-    <t>Weakly Supervised Explainable Phrasal Reasoning with Neural Fuzzy Logic</t>
-  </si>
-  <si>
-    <t>Analyzing differentiable fuzzy logic operators</t>
-  </si>
-  <si>
-    <t>Artif. Intell.</t>
-  </si>
-  <si>
-    <t>Vit-net: Interpretable vision transformers with neural tree decoder</t>
-  </si>
-  <si>
-    <t>Entropy-based logic explanations of neural networks</t>
-  </si>
-  <si>
-    <t>Extending Logic Explained Networks to Text Classification</t>
-  </si>
-  <si>
-    <t>Explainable Neural Rule Learning</t>
-  </si>
-  <si>
-    <t>Deep differentiable logic gate networks</t>
-  </si>
-  <si>
-    <t>Interpretable neural-symbolic concept reasoning</t>
-  </si>
-  <si>
-    <t>Learning to Binarize Continuous Features for Neuro-Rule Networks.</t>
-  </si>
-  <si>
-    <t>Learning interpretable rules for scalable data representation and classification</t>
-  </si>
-  <si>
-    <t>FINRule: Feature Interactive Neural Rule Learning</t>
-  </si>
-  <si>
     <t>CIKM</t>
   </si>
   <si>
-    <t>Logic explained networks</t>
-  </si>
-  <si>
-    <t>Convolutional Differentiable Logic Gate Networks</t>
-  </si>
-  <si>
-    <t>HyperLogic: Enhancing Diversity and Accuracy in Rule Learning with HyperNets</t>
+    <t>**Paper**</t>
+  </si>
+  <si>
+    <t>**Year**</t>
+  </si>
+  <si>
+    <t>**Venue**</t>
+  </si>
+  <si>
+    <t>[Rationalizing Neural Predictions](https://doi.org/10.18653/v1/d16-1011)</t>
+  </si>
+  <si>
+    <t>[From softmax to sparsemax: A sparse model of attention and multi-label classification](http://proceedings.mlr.press/v48/martins16.html)</t>
+  </si>
+  <si>
+    <t>[Neural interaction transparency (nit): Disentangling learned interactions for improved interpretability](https://proceedings.neurips.cc/paper/2018/hash/74378afe5e8b20910cf1f939e57f0480-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[INVASE: Instance-wise variable selection using neural networks](https://openreview.net/forum?id=BJg_roAcK7)</t>
+  </si>
+  <si>
+    <t>[Learning to explain: An information-theoretic perspective on model interpretation](http://proceedings.mlr.press/v80/chen18j.html)</t>
+  </si>
+  <si>
+    <t>[Approximating CNNs with Bag-of-local-Features models works surprisingly well on ImageNet](https://openreview.net/forum?id=SkfMWhAqYQ)</t>
+  </si>
+  <si>
+    <t>[Towards robust interpretability with self-explaining neural networks](https://proceedings.neurips.cc/paper/2018/hash/3e9f0fc9b2f89e043bc6233994dfcf76-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Beyond Polarity: Interpretable Financial Sentiment Analysis with Hierarchical Query-driven Attention](https://doi.org/10.24963/ijcai.2018/590)</t>
+  </si>
+  <si>
+    <t>[Interpretable multi-task learning for product quality prediction with attention mechanism](https://doi.org/10.1109/ICDE.2019.00207)</t>
+  </si>
+  <si>
+    <t>[Adaptively Sparse Transformers](https://doi.org/10.18653/v1/D19-1223)</t>
+  </si>
+  <si>
+    <t>[Exploiting kernel sparsity and entropy for interpretable CNN compression](http://openaccess.thecvf.com/content_CVPR_2019/html/Li_Exploiting_Kernel_Sparsity_and_Entropy_for_Interpretable_CNN_Compression_CVPR_2019_paper.html)</t>
+  </si>
+  <si>
+    <t>[Learning representations for neural network-based classification using the information bottleneck principle](https://doi.org/10.1109/TPAMI.2019.2909031)</t>
+  </si>
+  <si>
+    <t>[Interpretable predictive modeling for climate variables with weighted lasso](https://doi.org/10.1609/aaai.v33i01.33011385)</t>
+  </si>
+  <si>
+    <t>[Attention is not not Explanation](https://doi.org/10.18653/v1/n19-1357)</t>
+  </si>
+  <si>
+    <t>[Is Attention Interpretable?](https://doi.org/10.18653/v1/p19-1282)</t>
+  </si>
+  <si>
+    <t>[Concrete autoencoders: Differentiable feature selection and reconstruction](http://proceedings.mlr.press/v97/balin19a.html)</t>
+  </si>
+  <si>
+    <t>[Deepcoda: personalized interpretability for compositional health data](http://proceedings.mlr.press/v119/quinn20a.html)</t>
+  </si>
+  <si>
+    <t>[Graph Information Bottleneck for Subgraph Recognition](https://arxiv.org/abs/2010.05563)</t>
+  </si>
+  <si>
+    <t>[Sparse shrunk additive models](http://proceedings.mlr.press/v119/liu20b.html)</t>
+  </si>
+  <si>
+    <t>[MRI reconstruction with interpretable pixel-wise operations using reinforcement learning](https://doi.org/10.1609/aaai.v34i01.5423)</t>
+  </si>
+  <si>
+    <t>[Attention is Not Only a Weight: Analyzing Transformers with Vector Norms](https://arxiv.org/abs/2004.10102)</t>
+  </si>
+  <si>
+    <t>[Modeling users' behavior sequences with hierarchical explainable network for cross-domain fraud detection](https://doi.org/10.1145/3366423.3380172)</t>
+  </si>
+  <si>
+    <t>[Feature selection using stochastic gates](http://proceedings.mlr.press/v119/yamada20a.html)</t>
+  </si>
+  <si>
+    <t>[On Identifiability in Transformers](https://openreview.net/forum?id=BJg1f6EFDB)</t>
+  </si>
+  <si>
+    <t>[Consistent feature selection for analytic deep neural networks](https://proceedings.neurips.cc/paper/2020/hash/1959eb9d5a0f7ebc58ebde81d5df400d-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Towards Transparent and Explainable Attention Models](https://doi.org/10.18653/v1/2020.acl-main.387)</t>
+  </si>
+  <si>
+    <t>[Learning to Deceive with Attention-Based Explanations](https://doi.org/10.18653/v1/2020.acl-main.432)</t>
+  </si>
+  <si>
+    <t>[Timeshap: Explaining recurrent models through sequence perturbations](https://doi.org/10.1145/3447548.3467166)</t>
+  </si>
+  <si>
+    <t>[GAMI-Net: An explainable neural network based on generalized additive models with structured interactions](https://doi.org/10.1016/j.patcog.2021.108192)</t>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>[Shapley Explanation Networks](https://openreview.net/forum?id=vsU0efpivw)</t>
+  </si>
+  <si>
+    <t>[Market-oriented job skill valuation with cooperative composition neural network](https://www.nature.com/articles/s41467-021-22215-y)</t>
+  </si>
+  <si>
+    <t>Nature Communications</t>
+  </si>
+  <si>
+    <t>[Neural additive models: Interpretable machine learning with neural nets](https://proceedings.neurips.cc/paper/2021/hash/251bd0442dfcc53b5a761e050f8022b8-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Is Sparse Attention more Interpretable?](https://doi.org/10.18653/v1/2021.acl-short.17)</t>
+  </si>
+  <si>
+    <t>[Edge: Explaining deep reinforcement learning policies](https://proceedings.neurips.cc/paper/2021/hash/65c89f5a9501a04c073b354f03791b1f-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Why attentions may not be interpretable?](https://doi.org/10.1145/3447548.3467307)</t>
+  </si>
+  <si>
+    <t>[Attention-based interpretability with concept transformers](https://openreview.net/forum?id=kAa9eDS0RdO)</t>
+  </si>
+  <si>
+    <t>[Effective Attention Sheds Light On Interpretability](https://doi.org/10.18653/v1/2021.findings-acl.361)</t>
+  </si>
+  <si>
+    <t>[Self-Interpretable Model with Transformation Equivariant Interpretation](https://proceedings.neurips.cc/paper/2021/hash/1387a00f03b4b423e63127b08c261bdc-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Towards rigorous interpretations: a formalisation of feature attribution](http://proceedings.mlr.press/v139/afchar21a.html)</t>
+  </si>
+  <si>
+    <t>[Discerning decision-making process of deep neural networks with hierarchical voting transformation](https://proceedings.neurips.cc/paper/2021/hash/8f1fa0193ca2b5d2fa0695827d8270e9-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Recognizing predictive substructures with subgraph information bottleneck](https://arxiv.org/abs/2103.11155)</t>
+  </si>
+  <si>
+    <t>[Tabnet: Attentive interpretable tabular learning](https://doi.org/10.1609/aaai.v35i8.16826)</t>
+  </si>
+  <si>
+    <t>[Lassonet: A neural network with feature sparsity](https://jmlr.org/papers/v22/20-848.html)</t>
+  </si>
+  <si>
+    <t>[Convolutional dynamic alignment networks for interpretable classifications](https://openaccess.thecvf.com/content/CVPR2021/html/Bohle_Convolutional_Dynamic_Alignment_Networks_for_Interpretable_Classifications_CVPR_2021_paper.html)</t>
+  </si>
+  <si>
+    <t>[Have We Learned to Explain?: How Interpretability Methods Can Learn to Encode Predictions in their Interpretations](http://proceedings.mlr.press/v130/jethani21a.html)</t>
+  </si>
+  <si>
+    <t>[Evidence-aware hierarchical interactive attention networks for explainable claim verification](https://doi.org/10.24963/ijcai.2020/193)</t>
+  </si>
+  <si>
+    <t>[Towards improved and interpretable deep metric learning via attentive grouping](https://arxiv.org/abs/2011.08877)</t>
+  </si>
+  <si>
+    <t>[Supervising model attention with human explanations for robust natural language inference](https://doi.org/10.1609/aaai.v36i10.21386)</t>
+  </si>
+  <si>
+    <t>[Deep Variational Information Bottleneck](https://doi.org/10.3390/s23198093)</t>
+  </si>
+  <si>
+    <t>[Locally sparse neural networks for tabular biomedical data](https://proceedings.mlr.press/v162/yang22i.html)</t>
+  </si>
+  <si>
+    <t>[Self-explaining deep models with logic rule reasoning](http://papers.nips.cc/paper_files/paper/2022/hash/1548d98b62d3a4382a31ba77d89186cd-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Is attention explanation? an introduction to the debate](https://aclanthology.org/2022.jeptalnrecital-taln.45)</t>
+  </si>
+  <si>
+    <t>[Puregam: Learning an inherently pure additive model](https://doi.org/10.1145/3534678.3539256)</t>
+  </si>
+  <si>
+    <t>[Query and attention augmentation for knowledge-based explainable reasoning](https://doi.org/10.1109/CVPR52688.2022.01513)</t>
+  </si>
+  <si>
+    <t>[A diversified attention model for interpretable multiple clusterings](https://doi.org/10.1109/TKDE.2022.3218693)</t>
+  </si>
+  <si>
+    <t>[Interpretable and generalizable graph learning via stochastic attention mechanism](https://proceedings.mlr.press/v162/miao22a.html)</t>
+  </si>
+  <si>
+    <t>[Neural basis models for interpretability](http://papers.nips.cc/paper_files/paper/2022/hash/37da88965c016dca016514df0e420c72-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[B-cos networks: Alignment is all we need for interpretability](https://doi.org/10.1109/CVPR52688.2022.01008)</t>
+  </si>
+  <si>
+    <t>[Sparse interaction additive networks via feature interaction detection and sparse selection](http://papers.nips.cc/paper_files/paper/2022/hash/5a3674849d6d6d23ac088b9a2552f323-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Scalable interpretability via polynomials](http://papers.nips.cc/paper_files/paper/2022/hash/ee81a23d6b83ac15fbeb5b7a30934e0b-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Seat: stable and explainable attention](https://doi.org/10.1609/aaai.v37i11.26517)</t>
+  </si>
+  <si>
+    <t>[Interpretable bilinear attention network with domain adaptation improves drug--target prediction](https://doi.org/10.1038/s42256-022-00605-1)</t>
+  </si>
+  <si>
+    <t>Nature Machine Intelligence</t>
+  </si>
+  <si>
+    <t>[Extractive explanations for interpretable text ranking](https://doi.org/10.1145/3576924)</t>
+  </si>
+  <si>
+    <t>[Improving interpretability via explicit word interaction graph layer](https://doi.org/10.1609/aaai.v37i11.26586)</t>
+  </si>
+  <si>
+    <t>[Interpretable Geometric Deep Learning via Learnable Randomness Injection](https://openreview.net/forum?id=6u7mf9s2A9)</t>
+  </si>
+  <si>
+    <t>[N²AQ: Neural Attention Additive Model for Interpretable Multi-Agent Q-Learning](https://proceedings.mlr.press/v202/liu23be.html)</t>
+  </si>
+  <si>
+    <t>[Towards Faithful Neural Network Intrinsic Interpretation with Shapley Additive Self-Attribution](https://doi.org/10.48550/arXiv.2309.15559)</t>
+  </si>
+  <si>
+    <t>[The contextual lasso: Sparse linear models via deep neural networks](http://papers.nips.cc/paper_files/paper/2023/hash/3f226824426a4d6ae3d3efad8883fc53-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Learning Faithful Attention for Interpretable Classification of Crisis-Related Microblogs under Constrained Human Budget](https://doi.org/10.1145/3543507.3583861)</t>
+  </si>
+  <si>
+    <t>[Improving Neural Additive Models with Bayesian Principles](https://openreview.net/forum?id=0pSTzCnEmi)</t>
+  </si>
+  <si>
+    <t>[Sparse Neural Additive Model: Interpretable Deep Learning with Feature Selection via Group Sparsity](https://doi.org/10.1007/978-3-031-43418-1_21)</t>
+  </si>
+  <si>
+    <t>[CAT: Interpretable Concept-based Taylor Additive Models](https://doi.org/10.1145/3637528.3672020)</t>
+  </si>
+  <si>
+    <t>[B-cos Alignment for Inherently Interpretable CNNs and Vision Transformers](https://doi.org/10.1109/TPAMI.2024.3355155)</t>
+  </si>
+  <si>
+    <t>[ProtoGate: Prototype-based Neural Networks with Global-to-local Feature Selection for Tabular Biomedical Data](https://openreview.net/forum?id=07fSWltF6M)</t>
+  </si>
+  <si>
+    <t>[InterpreTabNet: Distilling Predictive Signals from Tabular Data by Salient Feature Interpretation](https://openreview.net/forum?id=or8BQ4ohGb)</t>
+  </si>
+  <si>
+    <t>[Interpretable prototype-based graph information bottleneck](http://papers.nips.cc/paper_files/paper/2023/hash/f224f056694bcfe465c5d84579785761-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Exgc: Bridging efficiency and explainability in graph condensation](https://doi.org/10.1145/3589334.3645551)</t>
+  </si>
+  <si>
+    <t>[Towards self-interpretable graph-level anomaly detection](http://papers.nips.cc/paper_files/paper/2023/hash/1c6f06863df46de009a7a41b41c95cad-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Tempme: Towards the explainability of temporal graph neural networks via motif discovery](http://papers.nips.cc/paper_files/paper/2023/hash/5c5bc3553815adb4d1a8a5b8701e41a9-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[NODE-GAM: Neural Generalized Additive Model for Interpretable Deep Learning](https://openreview.net/forum?id=g8NJR6fCCl8)</t>
+  </si>
+  <si>
+    <t>[GRAND-SLAMIN'Interpretable Additive Modeling with Structural Constraints](http://papers.nips.cc/paper_files/paper/2023/hash/c057cb81b8d3c67093427bf1c16a4e9f-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Propagation Structure-Aware Graph Transformer for Robust and Interpretable Fake News Detection](https://doi.org/10.1145/3637528.3672024)</t>
+  </si>
+  <si>
+    <t>[NAISR: A 3D Neural Additive Model for Interpretable Shape Representation](https://openreview.net/forum?id=wg8NPfeMF9)</t>
+  </si>
+  <si>
+    <t>[Comprehensive Attribution: Inherently Explainable Vision Model with Feature Detector](https://doi.org/10.1007/978-3-031-73004-7_12)</t>
+  </si>
+  <si>
+    <t>[Learning equations for extrapolation and control](http://proceedings.mlr.press/v80/sahoo18a.html)</t>
+  </si>
+  <si>
+    <t>[Integration of neural network-based symbolic regression in deep learning for scientific discovery](https://doi.org/10.1109/TNNLS.2020.3017010)</t>
+  </si>
+  <si>
+    <t>[Neural symbolic regression that scales](http://proceedings.mlr.press/v139/biggio21a.html)</t>
+  </si>
+  <si>
+    <t>[Symbolicgpt: A generative transformer model for symbolic regression](https://arxiv.org/abs/2106.14131)</t>
+  </si>
+  <si>
+    <t>[End-to-end symbolic regression with transformers](http://papers.nips.cc/paper_files/paper/2022/hash/42eb37cdbefd7abae0835f4b67548c39-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[A unified framework for deep symbolic regression](http://papers.nips.cc/paper_files/paper/2022/hash/dbca58f35bddc6e4003b2dd80e42f838-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Controllable neural symbolic regression](https://proceedings.mlr.press/v202/bendinelli23a.html)</t>
+  </si>
+  <si>
+    <t>[Deep Generative Symbolic Regression](https://openreview.net/forum?id=o7koEEMA1bR)</t>
+  </si>
+  <si>
+    <t>[Kan: Kolmogorov-arnold networks](https://doi.org/10.48550/arXiv.2404.19756)</t>
+  </si>
+  <si>
+    <t>[GINN-LP: A Growing Interpretable Neural Network for Discovering Multivariate Laurent Polynomial Equations](https://doi.org/10.1609/aaai.v38i13.29396)</t>
+  </si>
+  <si>
+    <t>[Concept bottleneck models](https://doi.org/10.48550/arXiv.2411.16512)</t>
+  </si>
+  <si>
+    <t>[Concept whitening for interpretable image recognition](https://doi.org/10.1038/s42256-020-00265-z)</t>
+  </si>
+  <si>
+    <t>[Explainable neural networks that simulate reasoning](https://doi.org/10.1038/s43588-021-00132-w)</t>
+  </si>
+  <si>
+    <t>Nature Computational Science</t>
+  </si>
+  <si>
+    <t>[Post-hoc Concept Bottleneck Models](https://doi.org/10.48550/arXiv.2205.15480)</t>
+  </si>
+  <si>
+    <t>[Concept embedding models: Beyond the accuracy-explainability trade-off](http://papers.nips.cc/paper_files/paper/2022/hash/867c06823281e506e8059f5c13a57f75-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Addressing leakage in concept bottleneck models](http://papers.nips.cc/paper_files/paper/2022/hash/944ecf65a46feb578a43abfd5cddd960-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Probabilistic Concept Bottleneck Models](https://proceedings.mlr.press/v202/kim23g.html)</t>
+  </si>
+  <si>
+    <t>[Learning to Intervene on Concept Bottlenecks](https://doi.org/10.48550/arXiv.2308.13453)</t>
+  </si>
+  <si>
+    <t>[Interactive concept bottleneck models](https://doi.org/10.1609/aaai.v37i5.25736)</t>
+  </si>
+  <si>
+    <t>[Label-free Concept Bottleneck Models](https://openreview.net/forum?id=FlCg47MNvBA)</t>
+  </si>
+  <si>
+    <t>[Language in a bottle: Language model guided concept bottlenecks for interpretable image classification](https://doi.org/10.1109/CVPR52729.2023.01839)</t>
+  </si>
+  <si>
+    <t>[Towards Trustable Skin Cancer Diagnosis via Rewriting Model's Decision](https://doi.org/10.1109/CVPR52729.2023.01113)</t>
+  </si>
+  <si>
+    <t>[Pantypes: Diverse Representatives for Self-Explainable Models](https://doi.org/10.1609/aaai.v38i12.29223)</t>
+  </si>
+  <si>
+    <t>[VLG-CBM: Training Concept Bottleneck Models with Vision-Language Guidance](https://doi.org/10.48550/arXiv.2408.01432)</t>
+  </si>
+  <si>
+    <t>[Energy-based concept bottleneck models: unifying prediction, concept intervention, and conditional interpretations](https://doi.org/10.48550/arXiv.2401.14142)</t>
+  </si>
+  <si>
+    <t>[Mica: Towards explainable skin lesion diagnosis via multi-level image-concept alignment](https://doi.org/10.1609/aaai.v38i2.27842)</t>
+  </si>
+  <si>
+    <t>[Relational Concept Bottleneck Models](https://lirias.kuleuven.be/retrieve/789506)</t>
+  </si>
+  <si>
+    <t>[Stochastic Concept Bottleneck Models](https://doi.org/10.48550/arXiv.2406.19272)</t>
+  </si>
+  <si>
+    <t>[Learning to receive help: Intervention-aware concept embedding models](http://papers.nips.cc/paper_files/paper/2023/hash/770cabd044c4eacb6dc5924d9a686dce-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Incremental residual concept bottleneck models](https://doi.org/10.1109/CVPR52733.2024.01049)</t>
+  </si>
+  <si>
+    <t>[Understanding Inter-Concept Relationships in Concept-Based Models](https://openreview.net/forum?id=JA6ThxAmth)</t>
+  </si>
+  <si>
+    <t>[Coarse-to-fine concept bottleneck models](https://hal.science/hal-04709806/)</t>
+  </si>
+  <si>
+    <t>[This looks like that: deep learning for interpretable image recognition](https://proceedings.neurips.cc/paper/2019/hash/adf7ee2dcf142b0e11888e72b43fcb75-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Interpretable and steerable sequence learning via prototypes](https://doi.org/10.1145/3292500.3330908)</t>
+  </si>
+  <si>
+    <t>[Neural prototype trees for interpretable fine-grained image recognition](https://openaccess.thecvf.com/content/CVPR2021/html/Nauta_Neural_Prototype_Trees_for_Interpretable_Fine-Grained_Image_Recognition_CVPR_2021_paper.html)</t>
+  </si>
+  <si>
+    <t>[Interpretable image recognition by constructing transparent embedding space](https://doi.org/10.1109/ICCV48922.2021.00093)</t>
+  </si>
+  <si>
+    <t>[Protopshare: Prototypical parts sharing for similarity discovery in interpretable image classification](https://doi.org/10.1145/3447548.3467245)</t>
+  </si>
+  <si>
+    <t>[XProtoNet: diagnosis in chest radiography with global and local explanations](https://openaccess.thecvf.com/content/CVPR2021/html/Kim_XProtoNet_Diagnosis_in_Chest_Radiography_With_Global_and_Local_Explanations_CVPR_2021_paper.html)</t>
+  </si>
+  <si>
+    <t>[Proto2Proto: Can you recognize the car, the way I do?](https://doi.org/10.1109/CVPR52688.2022.00999)</t>
+  </si>
+  <si>
+    <t>[Interpretable image classification with differentiable prototypes assignment](https://doi.org/10.1007/978-3-031-19775-8_21)</t>
+  </si>
+  <si>
+    <t>[Protgnn: Towards self-explaining graph neural networks](https://doi.org/10.1609/aaai.v36i8.20898)</t>
+  </si>
+  <si>
+    <t>[Protovae: A trustworthy self-explainable prototypical variational model](http://papers.nips.cc/paper_files/paper/2022/hash/722f3f9298a961d2639eadd3f14a2816-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[ProtoryNet-Interpretable Text Classification Via Prototype Trajectories](https://www.jmlr.org/papers/v24/21-0899.html)</t>
+  </si>
+  <si>
+    <t>[PIP-Net: Patch-Based Intuitive Prototypes for Interpretable Image Classification](https://doi.org/10.1109/CVPR52729.2023.00269)</t>
+  </si>
+  <si>
+    <t>[Towards interpretable deep reinforcement learning with human-friendly prototypes](https://openreview.net/forum?id=hWwY_Jq0xsN)</t>
+  </si>
+  <si>
+    <t>[Learning Support and Trivial Prototypes for Interpretable Image Classification](https://doi.org/10.1109/ICCV51070.2023.00197)</t>
+  </si>
+  <si>
+    <t>[Concept-level debugging of part-prototype networks](https://openreview.net/forum?id=oiwXWPDTyNk)</t>
+  </si>
+  <si>
+    <t>[Protoseg: Interpretable semantic segmentation with prototypical parts](https://doi.org/10.1109/WACV56688.2023.00153)</t>
+  </si>
+  <si>
+    <t>[This looks like those: Illuminating prototypical concepts using multiple visualizations](http://papers.nips.cc/paper_files/paper/2023/hash/7b76eea0c3683e440c3d362620f578cd-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Market-aware Long-term Job Skill Recommendation with Explainable Deep Reinforcement Learning](https://dl.acm.org/doi/abs/10.1145/3704998)</t>
+  </si>
+  <si>
+    <t>[Logic Tensor Networks for Semantic Image Interpretation](https://doi.org/10.24963/ijcai.2017/221)</t>
+  </si>
+  <si>
+    <t>[Deep neural decision trees](http://arxiv.org/abs/1806.06988)</t>
+  </si>
+  <si>
+    <t>[Deep neural networks constrained by decision rules](https://doi.org/10.1609/aaai.v33i01.33012496)</t>
+  </si>
+  <si>
+    <t>[NBDT: Neural-Backed Decision Tree](https://arxiv.org/abs/2004.00221)</t>
+  </si>
+  <si>
+    <t>[Transparent classification with multilayer logical perceptrons and random binarization](https://doi.org/10.1609/aaai.v34i04.6102)</t>
+  </si>
+  <si>
+    <t>[Human-driven FOL explanations of deep learning](https://doi.org/10.24963/ijcai.2020/309)</t>
+  </si>
+  <si>
+    <t>[A constraint-based approach to learning and explanation](https://doi.org/10.1609/aaai.v34i04.5774)</t>
+  </si>
+  <si>
+    <t>[Learning accurate and interpretable decision rule sets from neural networks](https://doi.org/10.1609/aaai.v35i5.16555)</t>
+  </si>
+  <si>
+    <t>[Scalable rule-based representation learning for interpretable classification](https://proceedings.neurips.cc/paper/2021/hash/ffbd6cbb019a1413183c8d08f2929307-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Weakly Supervised Explainable Phrasal Reasoning with Neural Fuzzy Logic](https://arxiv.org/abs/2109.08927)</t>
+  </si>
+  <si>
+    <t>[Analyzing differentiable fuzzy logic operators](https://doi.org/10.1016/j.artint.2021.103602)</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>[Vit-net: Interpretable vision transformers with neural tree decoder](https://proceedings.mlr.press/v162/kim22g.html)</t>
+  </si>
+  <si>
+    <t>[Entropy-based logic explanations of neural networks](https://doi.org/10.1609/aaai.v36i6.20551)</t>
+  </si>
+  <si>
+    <t>[Extending Logic Explained Networks to Text Classification](https://doi.org/10.18653/v1/2022.emnlp-main.604)</t>
+  </si>
+  <si>
+    <t>[Explainable Neural Rule Learning](https://doi.org/10.1145/3485447.3512023)</t>
+  </si>
+  <si>
+    <t>[Deep differentiable logic gate networks](http://papers.nips.cc/paper_files/paper/2022/hash/0d3496dd0cec77a999c98d35003203ca-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Interpretable neural-symbolic concept reasoning](https://proceedings.mlr.press/v202/barbiero23a.html)</t>
+  </si>
+  <si>
+    <t>[Learning to Binarize Continuous Features for Neuro-Rule Networks.](https://doi.org/10.24963/ijcai.2023/510)</t>
+  </si>
+  <si>
+    <t>[Learning interpretable rules for scalable data representation and classification](https://doi.org/10.48550/arXiv.2310.14336)</t>
+  </si>
+  <si>
+    <t>[FINRule: Feature Interactive Neural Rule Learning](https://doi.org/10.1145/3583780.3614884)</t>
+  </si>
+  <si>
+    <t>[Logic explained networks](https://doi.org/10.1016/j.artint.2022.103822)</t>
+  </si>
+  <si>
+    <t>[Convolutional Differentiable Logic Gate Networks](https://doi.org/10.48550/arXiv.2411.04732)</t>
+  </si>
+  <si>
+    <t>[HyperLogic: Enhancing Diversity and Accuracy in Rule Learning with HyperNets](https://openreview.net/forum?id=gJbZyKGfd6)</t>
+  </si>
+  <si>
+    <t>[Neural-symbolic VQA: Disentangling reasoning from vision and language understanding](https://proceedings.neurips.cc/paper/2018/hash/5e388103a391daabe3de1d76a6739ccd-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Pathologist-level interpretable whole-slide cancer diagnosis with deep learning](https://doi.org/10.1038/s42256-019-0052-1)</t>
+  </si>
+  <si>
+    <t>[Training interpretable convolutional neural networks by differentiating class-specific filters](https://doi.org/10.1007/978-3-030-58536-5_37)</t>
+  </si>
+  <si>
+    <t>[Interpretable CNNs for object classification](https://doi.org/10.1109/TPAMI.2020.2982882)</t>
+  </si>
+  <si>
+    <t>[Explainable object-induced action decision for autonomous vehicles](https://openaccess.thecvf.com/content_CVPR_2020/html/Xu_Explainable_Object-Induced_Action_Decision_for_Autonomous_Vehicles_CVPR_2020_paper.html)</t>
+  </si>
+  <si>
+    <t>[Interpretable compositional convolutional neural networks](https://doi.org/10.24963/ijcai.2021/409)</t>
+  </si>
+  <si>
+    <t>[Interpretable and Explainable Logical Policies via Neurally Guided Symbolic Abstraction](http://papers.nips.cc/paper_files/paper/2023/hash/9f42f06a54ce3b709ad78d34c73e4363-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[PICNN: A Pathway towards Interpretable Convolutional Neural Networks](https://doi.org/10.1609/aaai.v38i3.27971)</t>
+  </si>
+  <si>
+    <t>Paper Title</t>
+  </si>
+  <si>
+    <t>[Hierarchical attention networks for document classification](https://doi.org/10.18653/v1/n16-1174)</t>
+  </si>
+  <si>
+    <t>NAACL</t>
+  </si>
+  <si>
+    <t>[Learning deep features for discriminative localization](https://doi.org/10.1109/CVPR.2016.319)</t>
+  </si>
+  <si>
+    <t>[Learning to explain entity relationships in knowledge graphs](https://doi.org/10.3115/v1/p15-1055)</t>
+  </si>
+  <si>
+    <t>[Interpreting recurrent and attention-based neural models: a case study on natural language inference](https://aclanthology.org/D18-1537/)</t>
+  </si>
+  <si>
+    <t>[SPINE: Sparse interpretable neural embeddings](https://doi.org/10.1609/aaai.v32i1.11935)</t>
+  </si>
+  <si>
+    <t>[e-SNLI: Natural language inference with natural language explanations](https://proceedings.neurips.cc/paper/2018/hash/4c7a167bb329bd92580a99ce422d6fa6-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Towards Interpretable Natural Language Understanding with Explanations as Latent Variables](https://proceedings.neurips.cc/paper/2020/hash/4be2c8f27b8a420492f2d44463933eb6-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Interpretable neural predictions with differentiable binary variables](https://doi.org/10.18653/v1/p19-1284)</t>
+  </si>
+  <si>
+    <t>[Towards Explainable NLP: A Generative Explanation Framework for Text Classification](https://doi.org/10.18653/v1/p19-1560)</t>
+  </si>
+  <si>
+    <t>[Learning credible deep neural networks with rationale regularization](https://doi.org/10.1109/ICDM.2019.00025)</t>
+  </si>
+  <si>
+    <t>ICDM</t>
+  </si>
+  <si>
+    <t>[Explain Yourself! Leveraging Language Models for Commonsense Reasoning](https://doi.org/10.18653/v1/p19-1487)</t>
+  </si>
+  <si>
+    <t>[Protoattend: Attention-based prototypical learning](https://jmlr.org/papers/v21/20-042.html)</t>
+  </si>
+  <si>
+    <t>[WT5?! Training Text-to-Text Models to Explain their Predictions](https://arxiv.org/abs/2004.14546)</t>
+  </si>
+  <si>
+    <t>arXiv</t>
+  </si>
+  <si>
+    <t>[When Can Models Learn From Explanations? A Formal Framework for Understanding the Roles of Explanation Data](https://arxiv.org/abs/2102.02201)</t>
+  </si>
+  <si>
+    <t>[NILE: Natural Language Inference with Faithful Natural Language Explanations](https://doi.org/10.18653/v1/2020.acl-main.771)</t>
+  </si>
+  <si>
+    <t>[Chain-of-thought prompting elicits reasoning in large language models](http://papers.nips.cc/paper_files/paper/2022/hash/9d5609613524ecf4f15af0f7b31abca4-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Few-Shot Self-Rationalization with Natural Language Prompts](https://doi.org/10.18653/v1/2022.findings-naacl.31)</t>
+  </si>
+  <si>
+    <t>[ProtoryNet: Interpretable Text Classification Via Prototype Trajectories](http://jmlr.org/papers/v24/21-0899.html)</t>
+  </si>
+  <si>
+    <t>[LIREx: Augmenting Language Inference with Relevant Explanation](https://doi.org/10.1609/aaai.v35i16.17708)</t>
+  </si>
+  <si>
+    <t>[Summarize-then-Answer: Generating Concise Explanations for Multi-hop Reading Comprehension](https://doi.org/10.18653/v1/2021.emnlp-main.490)</t>
+  </si>
+  <si>
+    <t>[Tree of thoughts: Deliberate problem solving with large language models](http://papers.nips.cc/paper_files/paper/2023/hash/271db9922b8d1f4dd7aaef84ed5ac703-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[On Behalf of the Stakeholders: Trends in NLP Model Interpretability in the Era of LLMs](https://doi.org/10.48550/arXiv.2407.19200)</t>
+  </si>
+  <si>
+    <t>[How interpretable are reasoning explanations from prompting large language models?](https://doi.org/10.18653/v1/2024.findings-naacl.138)</t>
+  </si>
+  <si>
+    <t>[Are self-explanations from Large Language Models faithful?](https://doi.org/10.18653/v1/2024.findings-acl.19)</t>
+  </si>
+  <si>
+    <t>[Multi-objective molecule generation using interpretable substructures](http://proceedings.mlr.press/v119/jin20b.html)</t>
+  </si>
+  <si>
+    <t>[Explainable classification of brain networks via contrast subgraphs](https://doi.org/10.1145/3394486.3403383)</t>
+  </si>
+  <si>
+    <t>[Towards self-explainable graph neural network](https://doi.org/10.1145/3459637.3482306)</t>
+  </si>
+  <si>
+    <t>[Interpretable and efficient heterogeneous graph convolutional network](https://arxiv.org/abs/2005.13183)</t>
+  </si>
+  <si>
+    <t>[Improving subgraph recognition with variational graph information bottleneck](https://doi.org/10.1109/CVPR52688.2022.01879)</t>
+  </si>
+  <si>
+    <t>[Kergnns: Interpretable graph neural networks with graph kernels](https://doi.org/10.1609/aaai.v36i6.20615)</t>
+  </si>
+  <si>
+    <t>[Discovering Invariant Rationales for Graph Neural Networks](https://openreview.net/forum?id=hGXij5rfiHw)</t>
+  </si>
+  <si>
+    <t>[Train once and explain everywhere: Pre-training interpretable graph neural networks](http://papers.nips.cc/paper_files/paper/2023/hash/6ecd51685e2d765bc0ad32a2e73faf62-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[TECHS: Temporal logical graph networks for explainable extrapolation reasoning](https://doi.org/10.18653/v1/2023.acl-long.71)</t>
+  </si>
+  <si>
+    <t>[SIG: Efficient Self-Interpretable Graph Neural Network for Continuous-time Dynamic Graphs](https://doi.org/10.48550/arXiv.2405.19062)</t>
+  </si>
+  <si>
+    <t>[How Interpretable Are Interpretable Graph Neural Networks?](https://openreview.net/forum?id=F3G2udCF3Q)</t>
+  </si>
+  <si>
+    <t>[Globally Interpretable Graph Learning via Distribution Matching](https://doi.org/10.1145/3589334.3645674)</t>
+  </si>
+  <si>
+    <t>[Unveiling Global Interactive Patterns across Graphs: Towards Interpretable Graph Neural Networks](https://doi.org/10.1145/3637528.3671838)</t>
+  </si>
+  <si>
+    <t>[Interpretable graph networks formulate universal algebra conjectures](http://papers.nips.cc/paper_files/paper/2023/hash/2b2011a7d5396faf5899863d896a3c24-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[SES: Bridging the Gap Between Explainability and Prediction of Graph Neural Networks](https://doi.org/10.1109/ICDE60146.2024.00229)</t>
+  </si>
+  <si>
+    <t>[A Symbolic Rule Integration Framework with Logic Transformer for Inductive Relation Prediction](https://doi.org/10.1145/3589334.3645594)</t>
+  </si>
+  <si>
+    <t>[MMGNN: A Molecular Merged Graph Neural Network for Explainable Solvation Free Energy Prediction](https://www.ijcai.org/proceedings/2024/642)</t>
+  </si>
+  <si>
+    <t>[Towards better interpretability in deep q-networks](https://doi.org/10.1609/aaai.v33i01.33014561)</t>
+  </si>
+  <si>
+    <t>[Towards interpretable reinforcement learning using attention augmented agents](https://proceedings.neurips.cc/paper/2019/hash/e9510081ac30ffa83f10b68cde1cac07-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Alphastock: A buying-winners-and-selling-losers investment strategy using interpretable deep reinforcement attention networks](https://doi.org/10.1145/3292500.3330647)</t>
+  </si>
+  <si>
+    <t>[Self-supervised discovering of interpretable features for reinforcement learning](https://doi.org/10.1109/TPAMI.2020.3037898)</t>
+  </si>
+  <si>
+    <t>[What did you think would happen? explaining agent behaviour through intended outcomes](https://proceedings.neurips.cc/paper/2020/hash/d5ab8dc7ef67ca92e41d730982c5c602-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Learning tree interpretation from object representation for deep reinforcement learning](https://proceedings.neurips.cc/paper/2021/hash/a35fe7f7fe8217b4369a0af4244d1fca-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Differentiable logic policy for interpretable deep reinforcement learning](https://doi.org/10.1109/TPAMI.2023.3285634)</t>
+  </si>
+  <si>
+    <t>[Explainable reinforcement learning via a causal world model](https://doi.org/10.24963/ijcai.2023/505)</t>
+  </si>
+  <si>
+    <t>[ProtoX: Explaining a Reinforcement Learning Agent via Prototyping](http://papers.nips.cc/paper_files/paper/2022/hash/ae5bf4f35236240c9460e761c60fa53d-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Efficient Symbolic Policy Learning with Differentiable Symbolic Expression](http://papers.nips.cc/paper_files/paper/2023/hash/7207ffb9888068c0ee13ae3be023cada-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[Interpretable reward redistribution in reinforcement learning: a causal approach](http://papers.nips.cc/paper_files/paper/2023/hash/402e12102d6ec3ea3df40ce1b23d423a-Abstract-Conference.html)</t>
+  </si>
+  <si>
+    <t>[On completeness-aware concept-based explanations in deep neural networks](https://proceedings.neurips.cc/paper/2020/hash/ecb287ff763c169694f682af52c1f309-Abstract.html)</t>
+  </si>
+  <si>
+    <t>[Towards robust metrics for concept representation evaluation](https://doi.org/10.1609/aaai.v37i10.26392)</t>
+  </si>
+  <si>
+    <t>[Evaluation and improvement of interpretability for self-explainable part-prototype networks](https://doi.org/10.1109/ICCV51070.2023.00192)</t>
+  </si>
+  <si>
+    <t>[Towards human-centered explainable ai: A survey of user studies for model explanations](https://doi.org/10.1109/TPAMI.2023.3331846)</t>
+  </si>
+  <si>
+    <t>ACM TOIS</t>
+  </si>
+  <si>
+    <t>[Pixel-grounded prototypical part networks](https://doi.org/10.1109/WACV57701.2024.00470)</t>
+  </si>
+  <si>
+    <t>[Interpretability benchmark for evaluating spatial misalignment of prototypical parts explanations](https://doi.org/10.1609/aaai.v38i19.30154)</t>
+  </si>
+  <si>
+    <t>[Towards Modeling Uncertainties of Self-Explaining Neural Networks via Conformal Prediction](https://doi.org/10.1609/aaai.v38i13.29382)</t>
   </si>
 </sst>
 </file>
@@ -986,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D597EF-B3E6-4DE3-AD47-33AB211D4C6C}">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="89.109375" style="2" customWidth="1"/>
@@ -997,953 +1217,1166 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B2" s="1">
         <v>2016</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1">
         <v>2016</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1">
         <v>2018</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1">
         <v>2018</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1">
         <v>2018</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1">
         <v>2018</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B8" s="1">
         <v>2018</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1">
         <v>2018</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1">
         <v>2019</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B11" s="1">
         <v>2019</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1">
         <v>2019</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1">
         <v>2019</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1">
         <v>2019</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1">
         <v>2019</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1">
         <v>2019</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1">
         <v>2019</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1">
         <v>2020</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1">
         <v>2020</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1">
         <v>2020</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1">
         <v>2020</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B22" s="1">
         <v>2020</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B23" s="1">
         <v>2020</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B24" s="1">
         <v>2020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B25" s="1">
         <v>2020</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1">
         <v>2020</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B27" s="1">
         <v>2020</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B28" s="1">
         <v>2020</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B29" s="1">
         <v>2021</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B30" s="1">
         <v>2021</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="B31" s="1">
         <v>2021</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B32" s="1">
         <v>2021</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B33" s="1">
         <v>2021</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B34" s="1">
         <v>2021</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B35" s="1">
         <v>2021</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B36" s="1">
         <v>2021</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B37" s="1">
         <v>2021</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B38" s="1">
         <v>2021</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B39" s="1">
         <v>2021</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B40" s="1">
         <v>2021</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B41" s="1">
         <v>2021</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B42" s="1">
         <v>2021</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B43" s="1">
         <v>2021</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B44" s="1">
         <v>2021</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B45" s="1">
         <v>2021</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B46" s="1">
         <v>2021</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B47" s="1">
         <v>2021</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B48" s="1">
         <v>2022</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B49" s="1">
         <v>2022</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B50" s="1">
         <v>2022</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B51" s="1">
         <v>2022</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B52" s="1">
         <v>2022</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B53" s="1">
         <v>2022</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B54" s="1">
         <v>2022</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B55" s="1">
         <v>2022</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B56" s="1">
         <v>2022</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="2" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B57" s="1">
         <v>2022</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B58" s="1">
         <v>2022</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B59" s="1">
         <v>2022</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B60" s="1">
         <v>2022</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B61" s="1">
         <v>2022</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="2" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="B62" s="1">
         <v>2023</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="B63" s="1">
         <v>2023</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B64" s="1">
         <v>2023</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="2" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B65" s="1">
         <v>2023</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B66" s="1">
         <v>2023</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B67" s="1">
         <v>2023</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B68" s="1">
         <v>2023</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B69" s="1">
         <v>2023</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="2" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="B70" s="1">
         <v>2023</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="2" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="B71" s="1">
         <v>2023</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="2" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="B72" s="1">
         <v>2023</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="B73" s="1">
         <v>2024</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="2" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B74" s="1">
         <v>2024</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="2" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="B75" s="1">
         <v>2024</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>106</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="B76" s="1">
         <v>2024</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="B77" s="1">
         <v>2024</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B78" s="1">
         <v>2024</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B79" s="1">
         <v>2024</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>103</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="B80" s="1">
         <v>2024</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="B81" s="1">
         <v>2024</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B82" s="1">
         <v>2024</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B83" s="1">
         <v>2024</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="B84" s="1">
         <v>2024</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B85" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B86" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E236D282-7D07-459D-8A1A-A7E38CC613CD}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="72" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>238</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1959,134 +2392,134 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1">
       <c r="A1" s="4" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B2" s="3">
         <v>2018</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3">
         <v>2020</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B4" s="3">
         <v>2021</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B5" s="3">
         <v>2021</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B6" s="3">
         <v>2021</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B7" s="3">
         <v>2022</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B8" s="3">
         <v>2022</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B9" s="3">
         <v>2023</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B10" s="3">
         <v>2023</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="B11" s="3">
         <v>2024</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B12" s="3">
         <v>2024</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2101,282 +2534,282 @@
   <cols>
     <col min="1" max="1" width="77.33203125" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19" style="3" customWidth="1"/>
+    <col min="3" max="3" width="31" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B2" s="3">
         <v>2020</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B3" s="3">
         <v>2020</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3">
         <v>2021</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B5" s="3">
         <v>2021</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3">
         <v>2021</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B7" s="3">
         <v>2022</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B8" s="3">
         <v>2022</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B9" s="3">
         <v>2022</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B10" s="3">
         <v>2023</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B11" s="3">
         <v>2023</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B12" s="3">
         <v>2023</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B13" s="3">
         <v>2023</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B14" s="3">
         <v>2023</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B15" s="3">
         <v>2023</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B17" s="3">
         <v>2024</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B18" s="3">
         <v>2024</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B19" s="3">
         <v>2024</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B20" s="3">
         <v>2024</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B21" s="3">
         <v>2024</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B22" s="3">
         <v>2024</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B23" s="3">
         <v>2024</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B24" s="3">
         <v>2024</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B25" s="3">
         <v>2024</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2397,233 +2830,233 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B2" s="6">
         <v>2019</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B3" s="6">
         <v>2019</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B4" s="6">
         <v>2021</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B5" s="6">
         <v>2021</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>162</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B6" s="6">
         <v>2021</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B7" s="6">
         <v>2021</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B8" s="6">
         <v>2022</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B9" s="6">
         <v>2022</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B10" s="6">
         <v>2022</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B11" s="6">
         <v>2022</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B12" s="6">
         <v>2023</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B13" s="6">
         <v>2023</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B14" s="6">
         <v>2023</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B15" s="6">
         <v>2023</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>162</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B16" s="6">
         <v>2023</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B17" s="6">
         <v>2023</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B18" s="6">
         <v>2024</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B19" s="6">
         <v>2024</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B20" s="6">
         <v>2024</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B21" s="6">
         <v>2024</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2636,7 +3069,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8AC559-E88D-4497-86B1-27459ED35A67}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="67.5546875" customWidth="1"/>
@@ -2646,343 +3079,310 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B2" s="1">
         <v>2017</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B3" s="1">
         <v>2018</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B4" s="1">
         <v>2019</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B5" s="1">
         <v>2020</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B6" s="1">
         <v>2020</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B7" s="1">
         <v>2020</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B8" s="1">
         <v>2020</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B9" s="1">
         <v>2021</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B10" s="1">
         <v>2021</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B11" s="1">
         <v>2021</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B12" s="1">
         <v>2021</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B13" s="1">
         <v>2021</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B14" s="1">
         <v>2022</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B15" s="1">
         <v>2022</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B16" s="1">
         <v>2022</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B17" s="1">
         <v>2022</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B18" s="1">
         <v>2022</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B19" s="1">
         <v>2022</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B20" s="1">
         <v>2022</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B21" s="1">
         <v>2023</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B22" s="1">
         <v>2023</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B23" s="1">
         <v>2023</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B24" s="1">
         <v>2023</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>185</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="B25" s="1">
         <v>2023</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>3</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B26" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>175</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B27" s="1">
         <v>2024</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="B28" s="1">
         <v>2024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2992,36 +3392,1028 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F239EBE8-CDE7-4896-9887-C00407253A46}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="80.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="24.6640625" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12204874-28A7-4B36-A64C-71D71ECFE598}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="80.44140625" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="18.109375" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2016</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2016</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2016</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>216</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>218</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>221</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>222</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61AFBF71-C3F3-454D-A049-13E0D1909E3B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="70.77734375" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>237</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>238</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>239</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>241</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>242</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC09CE2B-4188-4AE4-9059-B79C3739FEF9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="66.5546875" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Paper Collections.xlsx
+++ b/Paper Collections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\Awesome-Interpretable-Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B55627-3E51-4D89-9482-CA6EBB03A244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF8EA06-F475-4FF4-8E0F-49F4CE09D495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4752" yWindow="120" windowWidth="24564" windowHeight="16152" firstSheet="1" activeTab="9" xr2:uid="{DC4A0462-C16D-4CCA-9144-463242733AF6}"/>
+    <workbookView xWindow="4752" yWindow="120" windowWidth="24564" windowHeight="16152" firstSheet="1" activeTab="6" xr2:uid="{DC4A0462-C16D-4CCA-9144-463242733AF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Attribution-based" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="407">
   <si>
     <t>EMNLP</t>
   </si>
@@ -78,12 +78,6 @@
     <t>ECCV</t>
   </si>
   <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Venue</t>
-  </si>
-  <si>
     <t>ICDE</t>
   </si>
   <si>
@@ -639,9 +633,6 @@
     <t>[PICNN: A Pathway towards Interpretable Convolutional Neural Networks](https://doi.org/10.1609/aaai.v38i3.27971)</t>
   </si>
   <si>
-    <t>Paper Title</t>
-  </si>
-  <si>
     <t>[Hierarchical attention networks for document classification](https://doi.org/10.18653/v1/n16-1174)</t>
   </si>
   <si>
@@ -829,6 +820,450 @@
   </si>
   <si>
     <t>[Towards Modeling Uncertainties of Self-Explaining Neural Networks via Conformal Prediction](https://doi.org/10.1609/aaai.v38i13.29382)</t>
+  </si>
+  <si>
+    <t>**Code**</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/taolei87/rcnn)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/deep-spin/entmax)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/vanderschaarlab/mlforhealthlabpub/tree/main/alg/invase)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/Jianbo-Lab/L2X)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/wielandbrendel/bag-of-local-features-models)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/amandavinci/senn)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/yuchaoli/KSE)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/google-research/google-research/tree/master/tabnet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/mfbalin/Concrete-Autoencoders)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/nphdang/DeepCoDA)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/Samyu0304/graph-information-bottleneck-for-Subgraph-Recognition)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/rhshi/sparse-rf)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/wentianli/MRI_RL)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/gorokoba560/norm-analysis-of-transformer)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/runopti/stg)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/LiamMaclean216/Pytorch-Transfomer)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/nusdbsystem/ARM-Net)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/akashkm99/Interpretable-Attention)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/danishpruthi/deceptive-attention)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/feedzai/timeshap)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/ZebinYang/gaminet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/inouye-lab/ShapleyExplanationNetworks)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/lemeln/nam)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/bzhangGo/zero)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/henrygwb/edge)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/kentaroy47/vision-transformers-cifar10)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/facebookresearch/e3b)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/xuanjieliu/self-supervised-learning-via-physical-symmetry)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/sunyinggilly/voten)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/ilemhadri/lassoNet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/moboehle/CoDA-Nets)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/rajesh-lab/realx)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/XinyiXuXD/DGML-master)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/joestacey/NLI_with_a_human_touch)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/Linear95/CLUB)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/jcyang34/lspin)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/archon159/selor)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/superjohnzhang/qaa)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/Graph-COM/GSAT)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/facebookresearch/nbm-spam)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/moboehle/b-cos)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/enouenj/sparse-interaction-additive-networks)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/peizhenbai/drugban)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/mrjleo/ranking-models)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/qdata/wigraph)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/graph-com/lri)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/fortuinlab/la-nam)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/vduong143/CAT-KDD-2024)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/b-cos/b-cos-v2)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/jacobyhsi/InterpreTabNet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/sang-woo-seo/pgib)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/yixinliu233/signet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/graph-and-geometric-learning/tempme)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/zzzace2000/nodegam)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/uncbiag/naisr)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/zood123/comet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/martius-lab/EQL)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/SymposiumOrganization/NeuralSymbolicRegressionThatScales)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/mojivalipour/symbolicgpt)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/facebookresearch/symbolicregression)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/samholt/deepgenerativesymbolicregression)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/rtqichen/torchdiffeq)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/kindxiaoming/pykan)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/google-research/google-research)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/marcotcr/lime-experiments)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/openai/CLIP)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/mateoespinosa/cem)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/trustworthy-ml-lab/vlg-cbm)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/ejkim47/prob-cbm)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/ml-research/cb2m)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/trustworthy-ml-lab/label-free-cbm)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/yueyang1996/labo)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/runedk93/pantypes)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/xmed-lab/ecbm)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/tommy-bie/mica)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/cfchen-duke/ProtoPNet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/myaooo/ProSeNet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/M-Nauta/ProtoTree)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/jackeywang96/tesnet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/hooman007/protoasnet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/archmaester/proto2proto)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/gmum/protopool)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/zaixizhang/protgnn)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/srishtigautam/protovae)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/dathong/ProtoryNet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/m-nauta/pipnet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/cwangrun/ST-ProtoPNet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/abonte/protopdebug)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/gmum/proto-segmentation)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/henrymachiyu/this-looks-like-those_protoconcepts)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/sbadredd/semantic-pascal-part)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/wOOL/DNDT)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/Jaraxxus-Me/LogiCity)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/alvinwan/neural-backed-decision-trees)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/microsoft/DiCE)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/pietrobarbiero/pytorch_explain)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/12wang3/rrl)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/manga-uofa/epr)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/HEmile/differentiable-fuzzy-logics)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/jumpsnack/ViT-NeT)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/pietrobarbiero/logic_explainer_networks)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/parrt/bookish)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/felix-petersen/difflogic)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/kexinyi/ns-vqa)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/hyliang96/CSGCNN)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/jacobgil/pytorch-grad-cam)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/Twizwei/bddoia_project)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/spdj2271/picnn)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/wengong-jin/multiobj-rationale)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/tlancian/contrast-subgraph)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/samyu0304/vgib)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/asfeng/kergnns)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/wuyxin/dir-gnn)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/2024sig/sig)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/Wangyuwen0627/GIP-Framework)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/maraghuram/I-DQN)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/cjlovering/Towards-Interpretable-Reinforcement-Learning-Using-Attention-Augmented-Agents-Replication)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/shiwj16/SSINet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/hmhyau/rl-intention)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/ZhengyaoJiang/NLRL)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/easeonway/explainable-causal-reinforcement-learning)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/soroush-bn/ProtoX)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/guojm14/ESPL)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/chihkuanyeh/concept_exp)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/mateoespinosa/concept-quality)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/hqhqaq/evalprotopnet)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/yaorong0921/hxai-survey)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/ematvey/hierarchical-attention-networks)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/zhoubolei/CAM)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/nickvosk/acl2015-dataset-learning-to-explain-entity-relationships)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/harsh19/SPINE)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/OanaMariaCamburu/e-SNLI)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/JamesHujy/ELV)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/bastings/interpretable_predictions)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/salesforce/cos-e)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/google-research/google-research/tree/master/protoattend)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/lesterpjy/numeric-t5)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/peterbhase/ExplanationRoles)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/SawanKumar28/nile)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/guidance-ai/guidance)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/allenai/feb)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/zhaoxy92/LIREx)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/stonybrooknlp/suqa)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/princeton-nlp/tree-of-thought-llm)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/wj210/cot_interpretability)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/fawazsammani/nlxgpt)</t>
   </si>
 </sst>
 </file>
@@ -1206,29 +1641,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D597EF-B3E6-4DE3-AD47-33AB211D4C6C}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="89.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.21875" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="37.109375" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="B2" s="1">
         <v>2016</v>
@@ -1236,10 +1675,13 @@
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1">
         <v>2016</v>
@@ -1247,10 +1689,13 @@
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1">
         <v>2018</v>
@@ -1258,10 +1703,13 @@
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
         <v>2018</v>
@@ -1269,10 +1717,13 @@
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1">
         <v>2018</v>
@@ -1280,10 +1731,13 @@
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1">
         <v>2018</v>
@@ -1291,10 +1745,13 @@
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1">
         <v>2018</v>
@@ -1302,10 +1759,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1">
         <v>2018</v>
@@ -1313,21 +1773,27 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1">
         <v>2019</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1">
         <v>2019</v>
@@ -1335,10 +1801,13 @@
       <c r="C11" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1">
         <v>2019</v>
@@ -1346,21 +1815,27 @@
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1">
         <v>2019</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1">
         <v>2019</v>
@@ -1368,10 +1843,13 @@
       <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1">
         <v>2019</v>
@@ -1379,10 +1857,13 @@
       <c r="C15" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1">
         <v>2019</v>
@@ -1390,10 +1871,13 @@
       <c r="C16" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1">
         <v>2019</v>
@@ -1401,10 +1885,13 @@
       <c r="C17" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1">
         <v>2020</v>
@@ -1412,10 +1899,13 @@
       <c r="C18" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1">
         <v>2020</v>
@@ -1423,10 +1913,13 @@
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1">
         <v>2020</v>
@@ -1434,10 +1927,13 @@
       <c r="C20" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1">
         <v>2020</v>
@@ -1445,10 +1941,13 @@
       <c r="C21" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="1">
         <v>2020</v>
@@ -1456,21 +1955,27 @@
       <c r="C22" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1">
         <v>2020</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>13</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B24" s="1">
         <v>2020</v>
@@ -1478,10 +1983,13 @@
       <c r="C24" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" s="1">
         <v>2020</v>
@@ -1489,10 +1997,13 @@
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B26" s="1">
         <v>2020</v>
@@ -1500,10 +2011,13 @@
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B27" s="1">
         <v>2020</v>
@@ -1511,10 +2025,13 @@
       <c r="C27" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" s="1">
         <v>2020</v>
@@ -1522,32 +2039,41 @@
       <c r="C28" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B29" s="1">
         <v>2021</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>14</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B30" s="1">
         <v>2021</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>55</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1">
         <v>2021</v>
@@ -1555,21 +2081,27 @@
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B32" s="1">
         <v>2021</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>58</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B33" s="1">
         <v>2021</v>
@@ -1577,10 +2109,13 @@
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B34" s="1">
         <v>2021</v>
@@ -1588,10 +2123,13 @@
       <c r="C34" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B35" s="1">
         <v>2021</v>
@@ -1599,21 +2137,27 @@
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B36" s="1">
         <v>2021</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>14</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B37" s="1">
         <v>2021</v>
@@ -1621,10 +2165,13 @@
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B38" s="1">
         <v>2021</v>
@@ -1632,10 +2179,13 @@
       <c r="C38" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B39" s="1">
         <v>2021</v>
@@ -1643,10 +2193,13 @@
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B40" s="1">
         <v>2021</v>
@@ -1654,10 +2207,13 @@
       <c r="C40" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="D40" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B41" s="1">
         <v>2021</v>
@@ -1665,21 +2221,27 @@
       <c r="C41" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B42" s="1">
         <v>2021</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B43" s="1">
         <v>2021</v>
@@ -1687,21 +2249,27 @@
       <c r="C43" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="D43" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B44" s="1">
         <v>2021</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B45" s="1">
         <v>2021</v>
@@ -1709,10 +2277,13 @@
       <c r="C45" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="D45" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B46" s="1">
         <v>2021</v>
@@ -1720,10 +2291,13 @@
       <c r="C46" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="D46" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B47" s="1">
         <v>2021</v>
@@ -1731,21 +2305,27 @@
       <c r="C47" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="D47" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B48" s="1">
         <v>2022</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B49" s="1">
         <v>2022</v>
@@ -1753,10 +2333,13 @@
       <c r="C49" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="D49" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B50" s="1">
         <v>2022</v>
@@ -1764,10 +2347,13 @@
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="D50" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B51" s="1">
         <v>2022</v>
@@ -1775,10 +2361,13 @@
       <c r="C51" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D51" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B52" s="1">
         <v>2022</v>
@@ -1786,10 +2375,13 @@
       <c r="C52" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="D52" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B53" s="1">
         <v>2022</v>
@@ -1797,10 +2389,13 @@
       <c r="C53" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="D53" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B54" s="1">
         <v>2022</v>
@@ -1808,10 +2403,13 @@
       <c r="C54" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="D54" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B55" s="1">
         <v>2022</v>
@@ -1819,21 +2417,27 @@
       <c r="C55" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="D55" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B56" s="1">
         <v>2022</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>18</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B57" s="1">
         <v>2022</v>
@@ -1841,10 +2445,13 @@
       <c r="C57" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="D57" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B58" s="1">
         <v>2022</v>
@@ -1852,10 +2459,13 @@
       <c r="C58" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="D58" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B59" s="1">
         <v>2022</v>
@@ -1863,10 +2473,13 @@
       <c r="C59" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="D59" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B60" s="1">
         <v>2022</v>
@@ -1874,10 +2487,13 @@
       <c r="C60" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="D60" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B61" s="1">
         <v>2022</v>
@@ -1885,10 +2501,13 @@
       <c r="C61" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="D61" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B62" s="1">
         <v>2023</v>
@@ -1896,32 +2515,41 @@
       <c r="C62" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="D62" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B63" s="1">
         <v>2023</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>90</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B64" s="1">
         <v>2023</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>17</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B65" s="1">
         <v>2023</v>
@@ -1929,10 +2557,13 @@
       <c r="C65" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B66" s="1">
         <v>2023</v>
@@ -1940,10 +2571,13 @@
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B67" s="1">
         <v>2023</v>
@@ -1951,21 +2585,27 @@
       <c r="C67" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B68" s="1">
         <v>2023</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B69" s="1">
         <v>2023</v>
@@ -1973,21 +2613,27 @@
       <c r="C69" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="D69" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B70" s="1">
         <v>2023</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>13</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B71" s="1">
         <v>2023</v>
@@ -1995,10 +2641,13 @@
       <c r="C71" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="D71" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B72" s="1">
         <v>2023</v>
@@ -2006,10 +2655,13 @@
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="D72" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B73" s="1">
         <v>2024</v>
@@ -2017,21 +2669,27 @@
       <c r="C73" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="D73" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B74" s="1">
         <v>2024</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B75" s="1">
         <v>2024</v>
@@ -2039,10 +2697,13 @@
       <c r="C75" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="D75" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B76" s="1">
         <v>2024</v>
@@ -2050,10 +2711,13 @@
       <c r="C76" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="D76" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B77" s="1">
         <v>2024</v>
@@ -2061,21 +2725,27 @@
       <c r="C77" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="D77" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B78" s="1">
         <v>2024</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>13</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B79" s="1">
         <v>2024</v>
@@ -2083,10 +2753,13 @@
       <c r="C79" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="D79" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B80" s="1">
         <v>2024</v>
@@ -2094,10 +2767,13 @@
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="D80" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B81" s="1">
         <v>2024</v>
@@ -2105,10 +2781,13 @@
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B82" s="1">
         <v>2024</v>
@@ -2116,10 +2795,13 @@
       <c r="C82" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="D82" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B83" s="1">
         <v>2024</v>
@@ -2127,10 +2809,13 @@
       <c r="C83" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="D83" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B84" s="1">
         <v>2024</v>
@@ -2138,16 +2823,22 @@
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="D84" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B85" s="1">
         <v>2025</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -2158,28 +2849,32 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E236D282-7D07-459D-8A1A-A7E38CC613CD}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="72" customWidth="1"/>
     <col min="2" max="2" width="7.44140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B2" s="3">
         <v>2018</v>
@@ -2187,10 +2882,13 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
         <v>2018</v>
@@ -2198,10 +2896,13 @@
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B4" s="3">
         <v>2020</v>
@@ -2209,10 +2910,13 @@
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3">
         <v>2021</v>
@@ -2220,10 +2924,13 @@
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B6" s="3">
         <v>2022</v>
@@ -2231,10 +2938,13 @@
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B7" s="3">
         <v>2022</v>
@@ -2242,10 +2952,13 @@
       <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B8" s="3">
         <v>2023</v>
@@ -2253,10 +2966,13 @@
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B9" s="3">
         <v>2023</v>
@@ -2264,54 +2980,69 @@
       <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B10" s="3">
         <v>2023</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B11" s="3">
         <v>2023</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B12" s="3">
         <v>2024</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>255</v>
+      </c>
+      <c r="D12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B13" s="3">
         <v>2024</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B14" s="3">
         <v>2024</v>
@@ -2319,10 +3050,13 @@
       <c r="C14" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B15" s="3">
         <v>2024</v>
@@ -2330,10 +3064,13 @@
       <c r="C15" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
@@ -2341,10 +3078,13 @@
       <c r="C16" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B17" s="3">
         <v>2024</v>
@@ -2352,10 +3092,13 @@
       <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B18" s="3">
         <v>2024</v>
@@ -2363,16 +3106,22 @@
       <c r="C18" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B19" s="3">
         <v>2024</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -2382,28 +3131,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FAC3A2B-668A-407B-AF2C-56674CEB10DA}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="93.5546875" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="3"/>
     <col min="3" max="3" width="21.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1">
+    <row r="1" spans="1:4" s="3" customFormat="1">
       <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B2" s="3">
         <v>2018</v>
@@ -2411,21 +3164,27 @@
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3">
         <v>2020</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B4" s="3">
         <v>2021</v>
@@ -2433,10 +3192,13 @@
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B5" s="3">
         <v>2021</v>
@@ -2444,21 +3206,27 @@
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B6" s="3">
         <v>2021</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B7" s="3">
         <v>2022</v>
@@ -2466,10 +3234,13 @@
       <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B8" s="3">
         <v>2022</v>
@@ -2477,10 +3248,13 @@
       <c r="C8" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3">
         <v>2023</v>
@@ -2488,10 +3262,13 @@
       <c r="C9" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B10" s="3">
         <v>2023</v>
@@ -2499,27 +3276,36 @@
       <c r="C10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B11" s="3">
         <v>2024</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B12" s="3">
         <v>2024</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -2529,28 +3315,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B132377C-8AE1-442B-A5C4-1805A89C2262}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="77.33203125" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" style="3" customWidth="1"/>
     <col min="3" max="3" width="31" style="3" customWidth="1"/>
+    <col min="4" max="4" width="41.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B2" s="3">
         <v>2020</v>
@@ -2558,21 +3348,27 @@
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3">
         <v>2020</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3">
         <v>2021</v>
@@ -2580,21 +3376,27 @@
       <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B5" s="3">
         <v>2021</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>126</v>
+      </c>
+      <c r="D5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6" s="3">
         <v>2021</v>
@@ -2602,10 +3404,13 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B7" s="3">
         <v>2022</v>
@@ -2613,10 +3418,13 @@
       <c r="C7" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B8" s="3">
         <v>2022</v>
@@ -2624,10 +3432,13 @@
       <c r="C8" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B9" s="3">
         <v>2022</v>
@@ -2635,10 +3446,13 @@
       <c r="C9" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" s="3">
         <v>2023</v>
@@ -2646,10 +3460,13 @@
       <c r="C10" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3">
         <v>2023</v>
@@ -2657,10 +3474,13 @@
       <c r="C11" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B12" s="3">
         <v>2023</v>
@@ -2668,10 +3488,13 @@
       <c r="C12" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B13" s="3">
         <v>2023</v>
@@ -2679,10 +3502,13 @@
       <c r="C13" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B14" s="3">
         <v>2023</v>
@@ -2690,10 +3516,13 @@
       <c r="C14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B15" s="3">
         <v>2023</v>
@@ -2701,10 +3530,13 @@
       <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
@@ -2712,10 +3544,13 @@
       <c r="C16" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B17" s="3">
         <v>2024</v>
@@ -2723,21 +3558,27 @@
       <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B18" s="3">
         <v>2024</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B19" s="3">
         <v>2024</v>
@@ -2745,10 +3586,13 @@
       <c r="C19" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B20" s="3">
         <v>2024</v>
@@ -2756,10 +3600,13 @@
       <c r="C20" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3">
         <v>2024</v>
@@ -2767,10 +3614,13 @@
       <c r="C21" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B22" s="3">
         <v>2024</v>
@@ -2778,10 +3628,13 @@
       <c r="C22" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B23" s="3">
         <v>2024</v>
@@ -2789,10 +3642,13 @@
       <c r="C23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B24" s="3">
         <v>2024</v>
@@ -2800,16 +3656,22 @@
       <c r="C24" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>2024</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -2819,29 +3681,33 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E68515-9F20-476E-990B-843B469A9BF4}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="96.44140625" style="7" customWidth="1"/>
     <col min="2" max="2" width="10.21875" style="6" customWidth="1"/>
     <col min="3" max="3" width="22" style="6" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="7"/>
+    <col min="4" max="4" width="32.88671875" style="7" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B2" s="6">
         <v>2019</v>
@@ -2849,21 +3715,27 @@
       <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="7" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B3" s="6">
         <v>2019</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>14</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B4" s="6">
         <v>2021</v>
@@ -2871,32 +3743,41 @@
       <c r="C4" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B5" s="6">
         <v>2021</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B6" s="6">
         <v>2021</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>14</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B7" s="6">
         <v>2021</v>
@@ -2904,10 +3785,13 @@
       <c r="C7" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B8" s="6">
         <v>2022</v>
@@ -2915,10 +3799,13 @@
       <c r="C8" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B9" s="6">
         <v>2022</v>
@@ -2926,10 +3813,13 @@
       <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B10" s="6">
         <v>2022</v>
@@ -2937,10 +3827,13 @@
       <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B11" s="6">
         <v>2022</v>
@@ -2948,21 +3841,27 @@
       <c r="C11" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B12" s="6">
         <v>2023</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B13" s="6">
         <v>2023</v>
@@ -2970,10 +3869,13 @@
       <c r="C13" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B14" s="6">
         <v>2023</v>
@@ -2981,21 +3883,27 @@
       <c r="C14" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B15" s="6">
         <v>2023</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B16" s="6">
         <v>2023</v>
@@ -3003,21 +3911,27 @@
       <c r="C16" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B17" s="6">
         <v>2023</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B18" s="6">
         <v>2024</v>
@@ -3025,10 +3939,13 @@
       <c r="C18" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B19" s="6">
         <v>2024</v>
@@ -3036,10 +3953,13 @@
       <c r="C19" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B20" s="6">
         <v>2024</v>
@@ -3047,19 +3967,25 @@
       <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B21" s="6">
         <v>2024</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="5"/>
     </row>
   </sheetData>
@@ -3069,28 +3995,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8AC559-E88D-4497-86B1-27459ED35A67}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="67.5546875" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="23" style="1" customWidth="1"/>
+    <col min="4" max="4" width="47.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B2" s="1">
         <v>2017</v>
@@ -3098,21 +4028,27 @@
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B3" s="1">
         <v>2018</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B4" s="1">
         <v>2019</v>
@@ -3120,10 +4056,13 @@
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B5" s="1">
         <v>2020</v>
@@ -3131,10 +4070,13 @@
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B6" s="1">
         <v>2020</v>
@@ -3142,10 +4084,13 @@
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B7" s="1">
         <v>2020</v>
@@ -3153,10 +4098,13 @@
       <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B8" s="1">
         <v>2020</v>
@@ -3164,10 +4112,13 @@
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B9" s="1">
         <v>2021</v>
@@ -3175,10 +4126,13 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B10" s="1">
         <v>2021</v>
@@ -3186,10 +4140,13 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B11" s="1">
         <v>2021</v>
@@ -3197,10 +4154,13 @@
       <c r="C11" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B12" s="1">
         <v>2021</v>
@@ -3208,10 +4168,13 @@
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" s="1">
         <v>2021</v>
@@ -3219,21 +4182,27 @@
       <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B14" s="1">
         <v>2022</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>175</v>
+      </c>
+      <c r="D14" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B15" s="1">
         <v>2022</v>
@@ -3241,10 +4210,13 @@
       <c r="C15" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B16" s="1">
         <v>2022</v>
@@ -3252,10 +4224,13 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B17" s="1">
         <v>2022</v>
@@ -3263,10 +4238,13 @@
       <c r="C17" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B18" s="1">
         <v>2022</v>
@@ -3274,21 +4252,27 @@
       <c r="C18" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B19" s="1">
         <v>2022</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B20" s="1">
         <v>2022</v>
@@ -3296,10 +4280,13 @@
       <c r="C20" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B21" s="1">
         <v>2023</v>
@@ -3307,10 +4294,13 @@
       <c r="C21" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B22" s="1">
         <v>2023</v>
@@ -3318,43 +4308,55 @@
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B23" s="1">
         <v>2023</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B24" s="1">
         <v>2023</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B25" s="1">
         <v>2023</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>175</v>
+      </c>
+      <c r="D25" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B26" s="1">
         <v>2024</v>
@@ -3362,10 +4364,13 @@
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B27" s="1">
         <v>2024</v>
@@ -3373,16 +4378,22 @@
       <c r="C27" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B28" s="1">
         <v>2024</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3392,28 +4403,32 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F239EBE8-CDE7-4896-9887-C00407253A46}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="80.109375" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="3"/>
     <col min="3" max="3" width="24.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="37.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B2" s="3">
         <v>2018</v>
@@ -3421,21 +4436,27 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B3" s="3">
         <v>2019</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3">
         <v>2020</v>
@@ -3443,10 +4464,13 @@
       <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B5" s="3">
         <v>2020</v>
@@ -3454,21 +4478,27 @@
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B6" s="3">
         <v>2020</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B7" s="3">
         <v>2020</v>
@@ -3476,10 +4506,13 @@
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B8" s="3">
         <v>2021</v>
@@ -3487,10 +4520,13 @@
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B9" s="3">
         <v>2021</v>
@@ -3498,10 +4534,13 @@
       <c r="C9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B10" s="3">
         <v>2023</v>
@@ -3509,10 +4548,13 @@
       <c r="C10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B11" s="3">
         <v>2023</v>
@@ -3520,10 +4562,13 @@
       <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B12" s="3">
         <v>2023</v>
@@ -3531,10 +4576,13 @@
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B13" s="3">
         <v>2023</v>
@@ -3542,21 +4590,27 @@
       <c r="C13" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B14" s="3">
         <v>2023</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B15" s="3">
         <v>2023</v>
@@ -3564,16 +4618,22 @@
       <c r="C15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -3583,28 +4643,32 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12204874-28A7-4B36-A64C-71D71ECFE598}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="3"/>
     <col min="3" max="3" width="18.109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="37.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>23</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" s="3">
         <v>2016</v>
@@ -3612,21 +4676,27 @@
       <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3">
         <v>2016</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>197</v>
+      </c>
+      <c r="D3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3">
         <v>2016</v>
@@ -3634,10 +4704,13 @@
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B5" s="3">
         <v>2016</v>
@@ -3645,10 +4718,13 @@
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B6" s="3">
         <v>2018</v>
@@ -3656,10 +4732,13 @@
       <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B7" s="3">
         <v>2018</v>
@@ -3667,10 +4746,13 @@
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3">
         <v>2018</v>
@@ -3678,10 +4760,13 @@
       <c r="C8" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>2018</v>
@@ -3689,10 +4774,13 @@
       <c r="C9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B10" s="3">
         <v>2018</v>
@@ -3700,10 +4788,13 @@
       <c r="C10" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B11" s="3">
         <v>2018</v>
@@ -3711,10 +4802,13 @@
       <c r="C11" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B12" s="3">
         <v>2019</v>
@@ -3722,21 +4816,27 @@
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B13" s="3">
         <v>2019</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>175</v>
+      </c>
+      <c r="D13" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B14" s="3">
         <v>2019</v>
@@ -3744,21 +4844,27 @@
       <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B15" s="3">
         <v>2019</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>207</v>
+      </c>
+      <c r="D15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B16" s="3">
         <v>2019</v>
@@ -3766,32 +4872,41 @@
       <c r="C16" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B17" s="3">
         <v>2020</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B18" s="3">
         <v>2020</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>211</v>
+      </c>
+      <c r="D18" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B19" s="3">
         <v>2022</v>
@@ -3799,10 +4914,13 @@
       <c r="C19" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B20" s="3">
         <v>2022</v>
@@ -3810,10 +4928,13 @@
       <c r="C20" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B21" s="3">
         <v>2022</v>
@@ -3821,32 +4942,41 @@
       <c r="C21" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B22" s="3">
         <v>2022</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>197</v>
+      </c>
+      <c r="D22" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B23" s="3">
         <v>2023</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B24" s="3">
         <v>2023</v>
@@ -3854,10 +4984,13 @@
       <c r="C24" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B25" s="3">
         <v>2023</v>
@@ -3865,10 +4998,13 @@
       <c r="C25" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B26" s="3">
         <v>2024</v>
@@ -3876,21 +5012,27 @@
       <c r="C26" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B27" s="3">
         <v>2024</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>211</v>
+      </c>
+      <c r="D27" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B28" s="3">
         <v>2024</v>
@@ -3898,16 +5040,22 @@
       <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B29" s="3">
         <v>2024</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -3917,28 +5065,32 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61AFBF71-C3F3-454D-A049-13E0D1909E3B}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="70.77734375" customWidth="1"/>
     <col min="2" max="2" width="14.5546875" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B2" s="3">
         <v>2020</v>
@@ -3946,10 +5098,13 @@
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B3" s="3">
         <v>2020</v>
@@ -3957,21 +5112,27 @@
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B4" s="3">
         <v>2021</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3">
         <v>2021</v>
@@ -3979,21 +5140,27 @@
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B6" s="3">
         <v>2021</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B7" s="3">
         <v>2022</v>
@@ -4001,10 +5168,13 @@
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B8" s="3">
         <v>2022</v>
@@ -4012,10 +5182,13 @@
       <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3">
         <v>2022</v>
@@ -4023,10 +5196,13 @@
       <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B10" s="3">
         <v>2022</v>
@@ -4034,10 +5210,13 @@
       <c r="C10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3">
         <v>2022</v>
@@ -4045,10 +5224,13 @@
       <c r="C11" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B12" s="3">
         <v>2023</v>
@@ -4056,10 +5238,13 @@
       <c r="C12" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B13" s="3">
         <v>2023</v>
@@ -4067,10 +5252,13 @@
       <c r="C13" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B14" s="3">
         <v>2023</v>
@@ -4078,10 +5266,13 @@
       <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B15" s="3">
         <v>2023</v>
@@ -4089,10 +5280,13 @@
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
@@ -4100,10 +5294,13 @@
       <c r="C16" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B17" s="3">
         <v>2024</v>
@@ -4111,10 +5308,13 @@
       <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B18" s="3">
         <v>2024</v>
@@ -4122,10 +5322,13 @@
       <c r="C18" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B19" s="3">
         <v>2024</v>
@@ -4133,10 +5336,13 @@
       <c r="C19" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B20" s="3">
         <v>2024</v>
@@ -4144,21 +5350,27 @@
       <c r="C20" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B21" s="3">
         <v>2024</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B22" s="3">
         <v>2024</v>
@@ -4166,10 +5378,13 @@
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B23" s="3">
         <v>2024</v>
@@ -4177,49 +5392,64 @@
       <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B24" s="3">
         <v>2024</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B25" s="3">
         <v>2024</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B26" s="3">
         <v>2024</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B27" s="3">
         <v>2024</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -4229,28 +5459,32 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC09CE2B-4188-4AE4-9059-B79C3739FEF9}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="66.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="39.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B2" s="3">
         <v>2019</v>
@@ -4258,10 +5492,13 @@
       <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B3" s="3">
         <v>2019</v>
@@ -4269,10 +5506,13 @@
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B4" s="3">
         <v>2019</v>
@@ -4280,21 +5520,27 @@
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B5" s="3">
         <v>2020</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B6" s="3">
         <v>2020</v>
@@ -4302,10 +5548,13 @@
       <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B7" s="3">
         <v>2021</v>
@@ -4313,10 +5562,13 @@
       <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3">
         <v>2021</v>
@@ -4324,21 +5576,27 @@
       <c r="C8" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B9" s="3">
         <v>2023</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B10" s="3">
         <v>2023</v>
@@ -4346,10 +5604,13 @@
       <c r="C10" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B11" s="3">
         <v>2023</v>
@@ -4357,10 +5618,13 @@
       <c r="C11" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B12" s="3">
         <v>2023</v>
@@ -4368,10 +5632,13 @@
       <c r="C12" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B13" s="3">
         <v>2023</v>
@@ -4379,10 +5646,13 @@
       <c r="C13" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B14" s="3">
         <v>2023</v>
@@ -4390,10 +5660,13 @@
       <c r="C14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B15" s="3">
         <v>2023</v>
@@ -4401,16 +5674,22 @@
       <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/Paper Collections.xlsx
+++ b/Paper Collections.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\Awesome-Interpretable-Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF8EA06-F475-4FF4-8E0F-49F4CE09D495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9391DC61-F6D0-4431-9465-DFA4364A9E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4752" yWindow="120" windowWidth="24564" windowHeight="16152" firstSheet="1" activeTab="6" xr2:uid="{DC4A0462-C16D-4CCA-9144-463242733AF6}"/>
+    <workbookView xWindow="4752" yWindow="120" windowWidth="24564" windowHeight="16152" firstSheet="1" activeTab="9" xr2:uid="{DC4A0462-C16D-4CCA-9144-463242733AF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Attribution-based" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="425">
   <si>
     <t>EMNLP</t>
   </si>
@@ -741,9 +741,6 @@
     <t>[TECHS: Temporal logical graph networks for explainable extrapolation reasoning](https://doi.org/10.18653/v1/2023.acl-long.71)</t>
   </si>
   <si>
-    <t>[SIG: Efficient Self-Interpretable Graph Neural Network for Continuous-time Dynamic Graphs](https://doi.org/10.48550/arXiv.2405.19062)</t>
-  </si>
-  <si>
     <t>[How Interpretable Are Interpretable Graph Neural Networks?](https://openreview.net/forum?id=F3G2udCF3Q)</t>
   </si>
   <si>
@@ -1167,9 +1164,6 @@
     <t>[Code](https://github.com/wuyxin/dir-gnn)</t>
   </si>
   <si>
-    <t>[Code](https://github.com/2024sig/sig)</t>
-  </si>
-  <si>
     <t>[Code](https://github.com/Wangyuwen0627/GIP-Framework)</t>
   </si>
   <si>
@@ -1264,6 +1258,66 @@
   </si>
   <si>
     <t>[Code](https://github.com/fawazsammani/nlxgpt)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/yangji721/SeSRDQN)</t>
+  </si>
+  <si>
+    <t>[Counterfactual Concept Bottleneck Models](https://openreview.net/forum?id=w7pMjyjsKN)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/gabriele-dominici/Counterfactual-CBM)</t>
+  </si>
+  <si>
+    <t>[Causal Concept Graph Models: Beyond Causal Opacity in Deep Learning](https://openreview.net/forum?id=lmKJ1b6PaL)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/gabriele-dominici/CausalCGM)</t>
+  </si>
+  <si>
+    <t>[Concept Bottleneck Large Language Models](https://openreview.net/forum?id=RC5FPYVQaH)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/Trustworthy-ML-Lab/CB-LLMs)</t>
+  </si>
+  <si>
+    <t>[Concept Bottleneck Language Models For protein design](https://openreview.net/forum?id=Yt9CFhOOFe)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/prescient-design/lobster)</t>
+  </si>
+  <si>
+    <t>[Restyling Unsupervised Concept Based Interpretable Networks with Generative Models](https://openreview.net/forum?id=CexatBp6rx)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/GnRlLeclerc/VisCoIN)</t>
+  </si>
+  <si>
+    <t>[Adaptive Concept Bottleneck for Foundation Models](https://openreview.net/forum?id=8sfc8MwG5v)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/jihyechoi77/CONDA)</t>
+  </si>
+  <si>
+    <t>[Lucid{PPN}: Unambiguous Prototypical Parts Network for User-centric Interpretable Computer Vision](https://openreview.net/forum?id=BM9qfolt6p)</t>
+  </si>
+  <si>
+    <t>[Intrinsic User-Centric Interpretability through Global Mixture of Experts](https://openreview.net/forum?id=wDcunIOAOk)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/epfl-ml4ed/interpretcc)</t>
+  </si>
+  <si>
+    <t>[Factor Graph-based Interpretable Neural Networks](https://openreview.net/forum?id=10DtLPsdro)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/yushuowiki/AGAIN)</t>
+  </si>
+  <si>
+    <t>[From {GNN}s to Trees: Multi-Granular Interpretability for Graph Neural Networks](https://openreview.net/forum?id=KEUPk0wXXe)</t>
+  </si>
+  <si>
+    <t>[Code](https://github.com/dutyj2020/TIF)</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D597EF-B3E6-4DE3-AD47-33AB211D4C6C}">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="89.109375" style="2" customWidth="1"/>
@@ -1662,7 +1716,7 @@
         <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1676,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1690,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1704,7 +1758,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1718,7 +1772,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1732,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1746,7 +1800,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1760,7 +1814,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1774,7 +1828,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1788,7 +1842,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1802,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1816,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1830,7 +1884,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1844,7 +1898,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1858,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1872,7 +1926,7 @@
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1886,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1900,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1914,7 +1968,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1928,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1942,7 +1996,7 @@
         <v>6</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1956,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1970,7 +2024,7 @@
         <v>13</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1984,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1998,7 +2052,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2012,7 +2066,7 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2026,7 +2080,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2040,7 +2094,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2054,7 +2108,7 @@
         <v>14</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2068,7 +2122,7 @@
         <v>55</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2082,7 +2136,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2096,7 +2150,7 @@
         <v>58</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2110,7 +2164,7 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2124,7 +2178,7 @@
         <v>7</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2138,7 +2192,7 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2152,7 +2206,7 @@
         <v>14</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2166,7 +2220,7 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2180,7 +2234,7 @@
         <v>7</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2194,7 +2248,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2208,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2222,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2236,7 +2290,7 @@
         <v>12</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2250,7 +2304,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2264,7 +2318,7 @@
         <v>15</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2278,7 +2332,7 @@
         <v>5</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2292,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2306,7 +2360,7 @@
         <v>4</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2320,7 +2374,7 @@
         <v>12</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2334,7 +2388,7 @@
         <v>6</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2348,7 +2402,7 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2362,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2376,7 +2430,7 @@
         <v>2</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2390,7 +2444,7 @@
         <v>7</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2404,7 +2458,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2418,7 +2472,7 @@
         <v>5</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2432,7 +2486,7 @@
         <v>18</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2446,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2460,7 +2514,7 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2474,7 +2528,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2488,7 +2542,7 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2502,7 +2556,7 @@
         <v>2</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2516,7 +2570,7 @@
         <v>6</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2530,7 +2584,7 @@
         <v>90</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2544,7 +2598,7 @@
         <v>17</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2558,7 +2612,7 @@
         <v>6</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2572,7 +2626,7 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2586,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2600,7 +2654,7 @@
         <v>16</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2614,7 +2668,7 @@
         <v>2</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2628,7 +2682,7 @@
         <v>13</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2642,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2656,7 +2710,7 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2670,7 +2724,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2684,7 +2738,7 @@
         <v>12</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2698,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2712,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2726,7 +2780,7 @@
         <v>2</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2740,7 +2794,7 @@
         <v>13</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2754,7 +2808,7 @@
         <v>2</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2768,7 +2822,7 @@
         <v>2</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2782,7 +2836,7 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2796,7 +2850,7 @@
         <v>2</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2810,7 +2864,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2824,7 +2878,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2838,7 +2892,21 @@
         <v>10</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B86" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -2869,12 +2937,12 @@
         <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B2" s="3">
         <v>2018</v>
@@ -2883,7 +2951,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2897,7 +2965,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2911,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2925,7 +2993,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2939,7 +3007,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2953,7 +3021,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2967,12 +3035,12 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B9" s="3">
         <v>2023</v>
@@ -2981,12 +3049,12 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B10" s="3">
         <v>2023</v>
@@ -2995,12 +3063,12 @@
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B11" s="3">
         <v>2023</v>
@@ -3009,7 +3077,7 @@
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3020,15 +3088,15 @@
         <v>2024</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D12" t="s">
-        <v>262</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B13" s="3">
         <v>2024</v>
@@ -3037,7 +3105,7 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3051,12 +3119,12 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B15" s="3">
         <v>2024</v>
@@ -3065,7 +3133,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3079,7 +3147,7 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3093,12 +3161,12 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B18" s="3">
         <v>2024</v>
@@ -3107,12 +3175,12 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B19" s="3">
         <v>2024</v>
@@ -3121,7 +3189,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3151,7 +3219,7 @@
         <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3165,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3179,7 +3247,7 @@
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3193,7 +3261,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3207,7 +3275,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3221,7 +3289,7 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3235,7 +3303,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3249,7 +3317,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3263,7 +3331,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3277,7 +3345,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3291,7 +3359,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3305,7 +3373,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3315,17 +3383,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B132377C-8AE1-442B-A5C4-1805A89C2262}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="77.33203125" customWidth="1"/>
+    <col min="1" max="1" width="77.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" style="3" customWidth="1"/>
     <col min="3" max="3" width="31" style="3" customWidth="1"/>
     <col min="4" max="4" width="41.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -3335,11 +3403,11 @@
         <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B2" s="3">
@@ -3349,11 +3417,11 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B3" s="3">
@@ -3363,11 +3431,11 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B4" s="3">
@@ -3377,11 +3445,11 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B5" s="3">
@@ -3391,11 +3459,11 @@
         <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B6" s="3">
@@ -3405,11 +3473,11 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="3">
@@ -3419,11 +3487,11 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="3">
@@ -3433,11 +3501,11 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B9" s="3">
@@ -3447,11 +3515,11 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B10" s="3">
@@ -3461,11 +3529,11 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B11" s="3">
@@ -3475,11 +3543,11 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B12" s="3">
@@ -3489,11 +3557,11 @@
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B13" s="3">
@@ -3503,11 +3571,11 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B14" s="3">
@@ -3517,11 +3585,11 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B15" s="3">
@@ -3531,11 +3599,11 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B16" s="3">
@@ -3545,11 +3613,11 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B17" s="3">
@@ -3559,11 +3627,11 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B18" s="3">
@@ -3573,11 +3641,11 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B19" s="3">
@@ -3587,11 +3655,11 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B20" s="3">
@@ -3601,11 +3669,11 @@
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B21" s="3">
@@ -3615,11 +3683,11 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
       <c r="B22" s="3">
@@ -3629,11 +3697,11 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>143</v>
       </c>
       <c r="B23" s="3">
@@ -3643,11 +3711,11 @@
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>144</v>
       </c>
       <c r="B24" s="3">
@@ -3657,11 +3725,11 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B25" s="3">
@@ -3671,11 +3739,96 @@
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>262</v>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B29" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B30" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B31" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3702,7 +3855,7 @@
         <v>25</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3716,7 +3869,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3730,7 +3883,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3744,7 +3897,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3758,7 +3911,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3772,7 +3925,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3786,7 +3939,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3800,7 +3953,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3814,7 +3967,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3828,7 +3981,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3842,7 +3995,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3856,7 +4009,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3870,7 +4023,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3884,7 +4037,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3898,7 +4051,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3912,7 +4065,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3926,7 +4079,7 @@
         <v>21</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3940,7 +4093,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3954,7 +4107,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3968,7 +4121,7 @@
         <v>2</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3982,11 +4135,22 @@
         <v>17</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>262</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="5"/>
+      <c r="A22" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B22" s="6">
+        <v>2025</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>261</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4015,7 +4179,7 @@
         <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4029,7 +4193,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4043,7 +4207,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4057,7 +4221,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4071,7 +4235,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4085,7 +4249,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4099,7 +4263,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4113,7 +4277,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4127,7 +4291,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4141,7 +4305,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4155,7 +4319,7 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4169,7 +4333,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4183,7 +4347,7 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4197,7 +4361,7 @@
         <v>175</v>
       </c>
       <c r="D14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4211,7 +4375,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4225,7 +4389,7 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4239,7 +4403,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4253,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4267,7 +4431,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4281,7 +4445,7 @@
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4295,7 +4459,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -4309,7 +4473,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4323,7 +4487,7 @@
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4337,7 +4501,7 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4351,7 +4515,7 @@
         <v>175</v>
       </c>
       <c r="D25" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4365,7 +4529,7 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -4379,7 +4543,7 @@
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -4393,7 +4557,7 @@
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -4423,7 +4587,7 @@
         <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4437,7 +4601,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4451,7 +4615,7 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4465,7 +4629,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4479,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4493,7 +4657,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4507,7 +4671,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4521,7 +4685,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4535,7 +4699,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4549,7 +4713,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4563,7 +4727,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4577,7 +4741,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4591,7 +4755,7 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4605,7 +4769,7 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4619,7 +4783,7 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4633,7 +4797,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -4663,7 +4827,7 @@
         <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4677,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4691,7 +4855,7 @@
         <v>197</v>
       </c>
       <c r="D3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4705,7 +4869,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4719,7 +4883,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4733,7 +4897,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4747,7 +4911,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4761,7 +4925,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4775,7 +4939,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4789,7 +4953,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4803,7 +4967,7 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4817,7 +4981,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4831,7 +4995,7 @@
         <v>175</v>
       </c>
       <c r="D13" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4845,7 +5009,7 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4859,7 +5023,7 @@
         <v>207</v>
       </c>
       <c r="D15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4873,7 +5037,7 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4887,7 +5051,7 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4901,7 +5065,7 @@
         <v>211</v>
       </c>
       <c r="D18" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4915,7 +5079,7 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4929,7 +5093,7 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4943,7 +5107,7 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -4957,7 +5121,7 @@
         <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4971,7 +5135,7 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4985,7 +5149,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4999,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5013,7 +5177,7 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5027,7 +5191,7 @@
         <v>211</v>
       </c>
       <c r="D27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -5041,7 +5205,7 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5055,7 +5219,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5065,10 +5229,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61AFBF71-C3F3-454D-A049-13E0D1909E3B}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="70.77734375" customWidth="1"/>
+    <col min="1" max="1" width="85.88671875" customWidth="1"/>
     <col min="2" max="2" width="14.5546875" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="35.6640625" customWidth="1"/>
@@ -5085,7 +5249,7 @@
         <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5099,7 +5263,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5113,7 +5277,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5127,7 +5291,7 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5141,7 +5305,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -5155,7 +5319,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5169,7 +5333,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5183,7 +5347,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5197,7 +5361,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5211,7 +5375,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -5225,7 +5389,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -5239,7 +5403,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5253,7 +5417,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5267,40 +5431,40 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>374</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>262</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B17" s="3">
         <v>2024</v>
@@ -5314,7 +5478,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B18" s="3">
         <v>2024</v>
@@ -5328,16 +5492,16 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>232</v>
       </c>
       <c r="B19" s="3">
         <v>2024</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>313</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -5348,10 +5512,10 @@
         <v>2024</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5362,10 +5526,10 @@
         <v>2024</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>262</v>
+        <v>373</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -5376,10 +5540,10 @@
         <v>2024</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>375</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5390,29 +5554,29 @@
         <v>2024</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3">
         <v>2024</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>237</v>
       </c>
       <c r="B25" s="3">
         <v>2024</v>
@@ -5421,7 +5585,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5432,24 +5596,38 @@
         <v>2024</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>239</v>
+        <v>421</v>
       </c>
       <c r="B27" s="3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>262</v>
+        <v>422</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>423</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -5479,12 +5657,12 @@
         <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B2" s="3">
         <v>2019</v>
@@ -5493,12 +5671,12 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B3" s="3">
         <v>2019</v>
@@ -5507,12 +5685,12 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B4" s="3">
         <v>2019</v>
@@ -5521,12 +5699,12 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B5" s="3">
         <v>2020</v>
@@ -5535,12 +5713,12 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B6" s="3">
         <v>2020</v>
@@ -5549,12 +5727,12 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B7" s="3">
         <v>2021</v>
@@ -5563,7 +5741,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5577,12 +5755,12 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B9" s="3">
         <v>2023</v>
@@ -5591,7 +5769,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -5605,12 +5783,12 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B11" s="3">
         <v>2023</v>
@@ -5619,12 +5797,12 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B12" s="3">
         <v>2023</v>
@@ -5633,7 +5811,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5647,7 +5825,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -5661,12 +5839,12 @@
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B15" s="3">
         <v>2023</v>
@@ -5675,12 +5853,12 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B16" s="3">
         <v>2024</v>
@@ -5689,7 +5867,7 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
